--- a/APLOS/POPResources/Templates/MlrBengali20181.xlsx
+++ b/APLOS/POPResources/Templates/MlrBengali20181.xlsx
@@ -1,37 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="22130"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25928"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\OfficeProject\APLOS.New\APLOS\POPResources\Templates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\AplosProject\APLOS\POPResources\Templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{324F8D8D-539E-40D9-B224-CA5858DEAF78}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66D73B83-0AC0-4963-B64D-C4047ACF98CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <externalReferences>
+    <externalReference r:id="rId2"/>
+  </externalReferences>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="59">
   <si>
     <t xml:space="preserve">কার্ড নং </t>
   </si>
@@ -162,21 +159,6 @@
     <t>{EmployeeNameLocal}</t>
   </si>
   <si>
-    <t>কল্যাণ কর্মকর্তা</t>
-  </si>
-  <si>
-    <t>ম্যানেজার (কমপ্লায়েনস)</t>
-  </si>
-  <si>
-    <t>ম্যানেজার  এইচ আর</t>
-  </si>
-  <si>
-    <t>জিএম  কমপ্লায়েনস</t>
-  </si>
-  <si>
-    <t>হিসাব রক্ষক</t>
-  </si>
-  <si>
     <t>{LegalDesignationLocal}</t>
   </si>
   <si>
@@ -199,16 +181,41 @@
   </si>
   <si>
     <t>{TotalAmount}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">প্রস্তুতকারী </t>
+  </si>
+  <si>
+    <t xml:space="preserve">পে-রোল অফিসার </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  নিরীক্ষণকারী</t>
+  </si>
+  <si>
+    <t xml:space="preserve">সিনিয়র ব্যবস্থাপক </t>
+  </si>
+  <si>
+    <t>অনুমোদনকারী /</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ওয়েলফেয়ার অফিসার </t>
+  </si>
+  <si>
+    <t>(প্রশাসন ও মানব সম্পদ বিভাগ)</t>
+  </si>
+  <si>
+    <t>সি. ই.ও</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="[$-5000445]###0;"/>
+    <numFmt numFmtId="165" formatCode="[$-5000445]###0.0;"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -251,6 +258,12 @@
       <color theme="1"/>
       <name val="RinkiyMJ"/>
     </font>
+    <font>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="SolaimanLipi"/>
+      <family val="4"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -278,7 +291,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="16">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -442,34 +455,17 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color indexed="64"/>
+      <top style="medium">
+        <color auto="1"/>
       </top>
-      <bottom style="hair">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="hair">
-        <color auto="1"/>
-      </left>
-      <right style="hair">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="hair">
-        <color auto="1"/>
-      </bottom>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -481,56 +477,44 @@
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -538,125 +522,104 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -892,6 +855,19 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="Sheet1"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1160,11 +1136,11 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q35"/>
+  <dimension ref="A1:Q33"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="37" style="4" hidden="1" customWidth="1"/>
-    <col min="2" max="2" width="21.28515625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="24.140625" style="2" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="19" style="2" customWidth="1"/>
     <col min="4" max="4" width="19.5703125" style="2" customWidth="1"/>
     <col min="5" max="5" width="23.28515625" style="2" customWidth="1"/>
@@ -1187,88 +1163,85 @@
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
-      <c r="J1" s="45"/>
-      <c r="K1" s="45"/>
-      <c r="L1" s="45"/>
-      <c r="M1" s="45"/>
-      <c r="N1" s="45"/>
-      <c r="O1" s="45"/>
+      <c r="J1" s="31"/>
+      <c r="K1" s="31"/>
+      <c r="L1" s="31"/>
+      <c r="M1" s="31"/>
+      <c r="N1" s="31"/>
+      <c r="O1" s="31"/>
     </row>
     <row r="2" spans="1:17" ht="46.5" customHeight="1">
       <c r="B2" s="5"/>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="45"/>
-      <c r="K2" s="45"/>
-      <c r="L2" s="45"/>
-      <c r="M2" s="45"/>
-      <c r="N2" s="45"/>
-      <c r="O2" s="45"/>
-    </row>
-    <row r="3" spans="1:17" s="12" customFormat="1" ht="24.95" customHeight="1">
-      <c r="B3" s="8"/>
-      <c r="C3" s="9"/>
-      <c r="D3" s="9"/>
-      <c r="E3" s="9"/>
-      <c r="F3" s="9"/>
-      <c r="G3" s="9"/>
-      <c r="H3" s="9"/>
-      <c r="I3" s="9"/>
-      <c r="J3" s="10"/>
-      <c r="K3" s="10"/>
-      <c r="L3" s="10"/>
-      <c r="M3" s="10"/>
-      <c r="N3" s="11"/>
-      <c r="O3" s="11"/>
-      <c r="P3" s="11"/>
-      <c r="Q3" s="11"/>
-    </row>
-    <row r="4" spans="1:17" s="12" customFormat="1" ht="24.95" customHeight="1">
-      <c r="B4" s="13"/>
-      <c r="C4" s="14"/>
-      <c r="D4" s="14"/>
-      <c r="E4" s="14"/>
-      <c r="F4" s="14"/>
-      <c r="G4" s="14"/>
-      <c r="H4" s="14"/>
-      <c r="I4" s="14"/>
-      <c r="J4" s="15"/>
-      <c r="K4" s="15"/>
-      <c r="L4" s="15"/>
-      <c r="M4" s="15"/>
-      <c r="N4" s="24"/>
-      <c r="O4" s="38" t="s">
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="J2" s="31"/>
+      <c r="K2" s="31"/>
+      <c r="L2" s="31"/>
+      <c r="M2" s="31"/>
+      <c r="N2" s="31"/>
+      <c r="O2" s="31"/>
+    </row>
+    <row r="3" spans="1:17" s="10" customFormat="1" ht="24.95" customHeight="1">
+      <c r="B3" s="6"/>
+      <c r="C3" s="7"/>
+      <c r="D3" s="7"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="7"/>
+      <c r="G3" s="7"/>
+      <c r="H3" s="7"/>
+      <c r="I3" s="7"/>
+      <c r="J3" s="8"/>
+      <c r="K3" s="8"/>
+      <c r="L3" s="8"/>
+      <c r="M3" s="8"/>
+      <c r="N3" s="9"/>
+      <c r="O3" s="9"/>
+      <c r="P3" s="9"/>
+      <c r="Q3" s="9"/>
+    </row>
+    <row r="4" spans="1:17" s="10" customFormat="1" ht="24.95" customHeight="1">
+      <c r="B4" s="11"/>
+      <c r="C4" s="12"/>
+      <c r="D4" s="12"/>
+      <c r="E4" s="12"/>
+      <c r="F4" s="12"/>
+      <c r="G4" s="12"/>
+      <c r="H4" s="12"/>
+      <c r="I4" s="12"/>
+      <c r="J4" s="13"/>
+      <c r="K4" s="13"/>
+      <c r="L4" s="13"/>
+      <c r="M4" s="13"/>
+      <c r="N4" s="20"/>
+      <c r="O4" s="41" t="s">
         <v>4</v>
       </c>
-      <c r="P4" s="38"/>
-      <c r="Q4" s="38"/>
+      <c r="P4" s="41"/>
+      <c r="Q4" s="41"/>
     </row>
     <row r="5" spans="1:17" ht="42" customHeight="1">
-      <c r="B5" s="46" t="s">
+      <c r="B5" s="36" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="46"/>
-      <c r="D5" s="46"/>
-      <c r="E5" s="46"/>
-      <c r="F5" s="46"/>
-      <c r="G5" s="46"/>
-      <c r="H5" s="46"/>
-      <c r="I5" s="46"/>
-      <c r="J5" s="46"/>
-      <c r="K5" s="46"/>
-      <c r="L5" s="46"/>
-      <c r="M5" s="46"/>
-      <c r="N5" s="46"/>
-      <c r="O5" s="46"/>
-      <c r="P5" s="46"/>
-      <c r="Q5" s="46"/>
-    </row>
-    <row r="6" spans="1:17" s="17" customFormat="1" ht="251.25" customHeight="1">
+      <c r="C5" s="36"/>
+      <c r="D5" s="36"/>
+      <c r="E5" s="36"/>
+      <c r="F5" s="36"/>
+      <c r="G5" s="36"/>
+      <c r="H5" s="36"/>
+      <c r="I5" s="36"/>
+      <c r="J5" s="36"/>
+      <c r="K5" s="36"/>
+      <c r="L5" s="36"/>
+      <c r="M5" s="36"/>
+      <c r="N5" s="36"/>
+      <c r="O5" s="36"/>
+      <c r="P5" s="36"/>
+      <c r="Q5" s="36"/>
+    </row>
+    <row r="6" spans="1:17" s="14" customFormat="1" ht="251.25" customHeight="1">
       <c r="B6" s="39" t="s">
         <v>18</v>
       </c>
@@ -1290,10 +1263,10 @@
       <c r="H6" s="39" t="s">
         <v>8</v>
       </c>
-      <c r="I6" s="47" t="s">
+      <c r="I6" s="37" t="s">
         <v>9</v>
       </c>
-      <c r="J6" s="48"/>
+      <c r="J6" s="38"/>
       <c r="K6" s="39" t="s">
         <v>10</v>
       </c>
@@ -1312,11 +1285,11 @@
       <c r="P6" s="39" t="s">
         <v>15</v>
       </c>
-      <c r="Q6" s="41" t="s">
+      <c r="Q6" s="42" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:17" s="18" customFormat="1" ht="93">
+    <row r="7" spans="1:17" s="15" customFormat="1" ht="93">
       <c r="B7" s="40"/>
       <c r="C7" s="40"/>
       <c r="D7" s="40"/>
@@ -1324,10 +1297,10 @@
       <c r="F7" s="40"/>
       <c r="G7" s="40"/>
       <c r="H7" s="40"/>
-      <c r="I7" s="30" t="s">
+      <c r="I7" s="23" t="s">
         <v>16</v>
       </c>
-      <c r="J7" s="30" t="s">
+      <c r="J7" s="23" t="s">
         <v>17</v>
       </c>
       <c r="K7" s="40"/>
@@ -1336,598 +1309,527 @@
       <c r="N7" s="44"/>
       <c r="O7" s="40"/>
       <c r="P7" s="40"/>
-      <c r="Q7" s="42"/>
-    </row>
-    <row r="8" spans="1:17" s="18" customFormat="1" ht="54" customHeight="1">
-      <c r="A8" s="18" t="s">
+      <c r="Q7" s="35"/>
+    </row>
+    <row r="8" spans="1:17" s="15" customFormat="1" ht="54" customHeight="1">
+      <c r="A8" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="36" t="s">
+      <c r="B8" s="34" t="s">
         <v>42</v>
       </c>
-      <c r="C8" s="36" t="s">
+      <c r="C8" s="34" t="s">
+        <v>43</v>
+      </c>
+      <c r="D8" s="34" t="s">
+        <v>27</v>
+      </c>
+      <c r="E8" s="34" t="s">
+        <v>45</v>
+      </c>
+      <c r="F8" s="34" t="s">
+        <v>44</v>
+      </c>
+      <c r="G8" s="34" t="s">
+        <v>28</v>
+      </c>
+      <c r="H8" s="34" t="s">
+        <v>49</v>
+      </c>
+      <c r="I8" s="34" t="s">
         <v>48</v>
       </c>
-      <c r="D8" s="36" t="s">
-        <v>27</v>
-      </c>
-      <c r="E8" s="36" t="s">
+      <c r="J8" s="34" t="s">
+        <v>30</v>
+      </c>
+      <c r="K8" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="L8" s="34" t="s">
+        <v>29</v>
+      </c>
+      <c r="M8" s="34" t="s">
+        <v>32</v>
+      </c>
+      <c r="N8" s="24" t="s">
+        <v>25</v>
+      </c>
+      <c r="O8" s="23" t="s">
+        <v>33</v>
+      </c>
+      <c r="P8" s="16"/>
+      <c r="Q8" s="16"/>
+    </row>
+    <row r="9" spans="1:17" s="15" customFormat="1" ht="72" customHeight="1">
+      <c r="A9" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" s="35"/>
+      <c r="C9" s="35"/>
+      <c r="D9" s="35"/>
+      <c r="E9" s="35"/>
+      <c r="F9" s="35"/>
+      <c r="G9" s="35"/>
+      <c r="H9" s="35"/>
+      <c r="I9" s="35"/>
+      <c r="J9" s="35"/>
+      <c r="K9" s="35"/>
+      <c r="L9" s="35"/>
+      <c r="M9" s="35"/>
+      <c r="N9" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="O9" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="P9" s="16"/>
+      <c r="Q9" s="16"/>
+    </row>
+    <row r="10" spans="1:17" s="15" customFormat="1" ht="28.5" customHeight="1">
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
+      <c r="G10" s="1"/>
+      <c r="H10" s="29"/>
+      <c r="I10" s="29"/>
+      <c r="J10" s="29"/>
+      <c r="K10" s="29"/>
+      <c r="L10" s="29"/>
+      <c r="M10" s="29"/>
+      <c r="N10" s="29"/>
+      <c r="O10" s="29"/>
+      <c r="P10" s="29"/>
+      <c r="Q10" s="32"/>
+    </row>
+    <row r="11" spans="1:17" s="18" customFormat="1" ht="55.5" customHeight="1">
+      <c r="A11" s="17" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="C11" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="D11" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="E11" s="21" t="s">
+        <v>22</v>
+      </c>
+      <c r="F11" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="G11" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="H11" s="31"/>
+      <c r="I11" s="31"/>
+      <c r="J11" s="31"/>
+      <c r="K11" s="31"/>
+      <c r="L11" s="31"/>
+      <c r="M11" s="31"/>
+      <c r="N11" s="31"/>
+      <c r="O11" s="31"/>
+      <c r="P11" s="31"/>
+      <c r="Q11" s="33"/>
+    </row>
+    <row r="12" spans="1:17" s="15" customFormat="1" ht="56.25" customHeight="1">
+      <c r="A12" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="B12" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="C12" s="25" t="s">
+        <v>36</v>
+      </c>
+      <c r="D12" s="25" t="s">
+        <v>47</v>
+      </c>
+      <c r="E12" s="25" t="s">
+        <v>35</v>
+      </c>
+      <c r="F12" s="25" t="s">
+        <v>37</v>
+      </c>
+      <c r="G12" s="25" t="s">
         <v>50</v>
       </c>
-      <c r="F8" s="36" t="s">
-        <v>49</v>
-      </c>
-      <c r="G8" s="36" t="s">
-        <v>28</v>
-      </c>
-      <c r="H8" s="36" t="s">
+      <c r="H12" s="31"/>
+      <c r="I12" s="31"/>
+      <c r="J12" s="31"/>
+      <c r="K12" s="31"/>
+      <c r="L12" s="31"/>
+      <c r="M12" s="31"/>
+      <c r="N12" s="31"/>
+      <c r="O12" s="31"/>
+      <c r="P12" s="31"/>
+      <c r="Q12" s="33"/>
+    </row>
+    <row r="13" spans="1:17" s="15" customFormat="1" ht="36.75" customHeight="1">
+      <c r="B13" s="27"/>
+      <c r="C13" s="27"/>
+      <c r="D13" s="27"/>
+      <c r="E13" s="27"/>
+      <c r="F13" s="27"/>
+      <c r="G13" s="27"/>
+      <c r="H13" s="31"/>
+      <c r="I13" s="31"/>
+      <c r="J13" s="31"/>
+      <c r="K13" s="31"/>
+      <c r="L13" s="31"/>
+      <c r="M13" s="31"/>
+      <c r="N13" s="31"/>
+      <c r="O13" s="31"/>
+      <c r="P13" s="31"/>
+      <c r="Q13" s="33"/>
+    </row>
+    <row r="14" spans="1:17" s="15" customFormat="1" ht="30.75" customHeight="1">
+      <c r="B14" s="27"/>
+      <c r="C14" s="27"/>
+      <c r="D14" s="27"/>
+      <c r="E14" s="27"/>
+      <c r="F14" s="27"/>
+      <c r="G14" s="27"/>
+      <c r="H14" s="31"/>
+      <c r="I14" s="31"/>
+      <c r="J14" s="31"/>
+      <c r="K14" s="31"/>
+      <c r="L14" s="31"/>
+      <c r="M14" s="31"/>
+      <c r="N14" s="31"/>
+      <c r="O14" s="31"/>
+      <c r="P14" s="31"/>
+      <c r="Q14" s="33"/>
+    </row>
+    <row r="15" spans="1:17" s="15" customFormat="1" ht="24.95" customHeight="1">
+      <c r="B15" s="27"/>
+      <c r="C15" s="27"/>
+      <c r="D15" s="27"/>
+      <c r="E15" s="27"/>
+      <c r="F15" s="27"/>
+      <c r="G15" s="27"/>
+      <c r="H15" s="31"/>
+      <c r="I15" s="31"/>
+      <c r="J15" s="31"/>
+      <c r="K15" s="31"/>
+      <c r="L15" s="31"/>
+      <c r="M15" s="31"/>
+      <c r="N15" s="31"/>
+      <c r="O15" s="31"/>
+      <c r="P15" s="31"/>
+      <c r="Q15" s="33"/>
+    </row>
+    <row r="16" spans="1:17" s="15" customFormat="1" ht="24.95" customHeight="1">
+      <c r="B16" s="27"/>
+      <c r="C16" s="27"/>
+      <c r="D16" s="27"/>
+      <c r="E16" s="27"/>
+      <c r="F16" s="27"/>
+      <c r="G16" s="27"/>
+      <c r="H16" s="31"/>
+      <c r="I16" s="31"/>
+      <c r="J16" s="31"/>
+      <c r="K16" s="31"/>
+      <c r="L16" s="31"/>
+      <c r="M16" s="31"/>
+      <c r="N16" s="31"/>
+      <c r="O16" s="31"/>
+      <c r="P16" s="31"/>
+      <c r="Q16" s="33"/>
+    </row>
+    <row r="17" spans="2:17" s="15" customFormat="1" ht="24.95" customHeight="1">
+      <c r="B17" s="27"/>
+      <c r="C17" s="27"/>
+      <c r="D17" s="27"/>
+      <c r="E17" s="27"/>
+      <c r="F17" s="27"/>
+      <c r="G17" s="27"/>
+      <c r="H17" s="31"/>
+      <c r="I17" s="31"/>
+      <c r="J17" s="31"/>
+      <c r="K17" s="31"/>
+      <c r="L17" s="31"/>
+      <c r="M17" s="31"/>
+      <c r="N17" s="31"/>
+      <c r="O17" s="31"/>
+      <c r="P17" s="31"/>
+      <c r="Q17" s="33"/>
+    </row>
+    <row r="18" spans="2:17" s="15" customFormat="1" ht="24.95" customHeight="1">
+      <c r="B18" s="27"/>
+      <c r="C18" s="27"/>
+      <c r="D18" s="27"/>
+      <c r="E18" s="27"/>
+      <c r="F18" s="27"/>
+      <c r="G18" s="27"/>
+      <c r="H18" s="31"/>
+      <c r="I18" s="31"/>
+      <c r="J18" s="31"/>
+      <c r="K18" s="31"/>
+      <c r="L18" s="31"/>
+      <c r="M18" s="31"/>
+      <c r="N18" s="31"/>
+      <c r="O18" s="31"/>
+      <c r="P18" s="31"/>
+      <c r="Q18" s="33"/>
+    </row>
+    <row r="19" spans="2:17" s="15" customFormat="1" ht="24.95" customHeight="1">
+      <c r="B19" s="27"/>
+      <c r="C19" s="27"/>
+      <c r="D19" s="27"/>
+      <c r="E19" s="27"/>
+      <c r="F19" s="27"/>
+      <c r="G19" s="27"/>
+      <c r="H19" s="31"/>
+      <c r="I19" s="31"/>
+      <c r="J19" s="31"/>
+      <c r="K19" s="31"/>
+      <c r="L19" s="31"/>
+      <c r="M19" s="31"/>
+      <c r="N19" s="31"/>
+      <c r="O19" s="31"/>
+      <c r="P19" s="31"/>
+      <c r="Q19" s="33"/>
+    </row>
+    <row r="20" spans="2:17" s="15" customFormat="1" ht="24.75" customHeight="1">
+      <c r="B20" s="28"/>
+      <c r="C20" s="29"/>
+      <c r="D20" s="29"/>
+      <c r="E20" s="29"/>
+      <c r="F20" s="29"/>
+      <c r="G20" s="29"/>
+      <c r="H20" s="31"/>
+      <c r="I20" s="31"/>
+      <c r="J20" s="31"/>
+      <c r="K20" s="31"/>
+      <c r="L20" s="31"/>
+      <c r="M20" s="31"/>
+      <c r="N20" s="31"/>
+      <c r="O20" s="31"/>
+      <c r="P20" s="31"/>
+      <c r="Q20" s="33"/>
+    </row>
+    <row r="21" spans="2:17" s="15" customFormat="1" ht="24.75" customHeight="1">
+      <c r="B21" s="30"/>
+      <c r="C21" s="31"/>
+      <c r="D21" s="31"/>
+      <c r="E21" s="31"/>
+      <c r="F21" s="31"/>
+      <c r="G21" s="31"/>
+      <c r="H21" s="19"/>
+      <c r="I21" s="19"/>
+      <c r="J21" s="19"/>
+      <c r="K21" s="19"/>
+      <c r="L21" s="19"/>
+      <c r="M21" s="19"/>
+      <c r="N21" s="19"/>
+      <c r="O21" s="19"/>
+      <c r="P21" s="19"/>
+      <c r="Q21" s="26"/>
+    </row>
+    <row r="22" spans="2:17" s="15" customFormat="1" ht="24.75" customHeight="1">
+      <c r="B22" s="30"/>
+      <c r="C22" s="31"/>
+      <c r="D22" s="31"/>
+      <c r="E22" s="31"/>
+      <c r="F22" s="31"/>
+      <c r="G22" s="31"/>
+      <c r="H22" s="19"/>
+      <c r="I22" s="19"/>
+      <c r="J22" s="19"/>
+      <c r="K22" s="19"/>
+      <c r="L22" s="19"/>
+      <c r="M22" s="19"/>
+      <c r="N22" s="19"/>
+      <c r="O22" s="19"/>
+      <c r="P22" s="19"/>
+      <c r="Q22" s="26"/>
+    </row>
+    <row r="23" spans="2:17" s="15" customFormat="1" ht="24.75" customHeight="1">
+      <c r="B23" s="30"/>
+      <c r="C23" s="31"/>
+      <c r="D23" s="31"/>
+      <c r="E23" s="31"/>
+      <c r="F23" s="31"/>
+      <c r="G23" s="31"/>
+      <c r="H23" s="19"/>
+      <c r="I23" s="19"/>
+      <c r="J23" s="19"/>
+      <c r="K23" s="19"/>
+      <c r="L23" s="19"/>
+      <c r="M23" s="19"/>
+      <c r="N23" s="19"/>
+      <c r="O23" s="19"/>
+      <c r="P23" s="19"/>
+      <c r="Q23" s="26"/>
+    </row>
+    <row r="24" spans="2:17" s="15" customFormat="1" ht="24.75" customHeight="1">
+      <c r="B24" s="30"/>
+      <c r="C24" s="31"/>
+      <c r="D24" s="31"/>
+      <c r="E24" s="31"/>
+      <c r="F24" s="31"/>
+      <c r="G24" s="31"/>
+      <c r="H24" s="19"/>
+      <c r="I24" s="19"/>
+      <c r="J24" s="19"/>
+      <c r="K24" s="19"/>
+      <c r="L24" s="19"/>
+      <c r="M24" s="19"/>
+      <c r="N24" s="19"/>
+      <c r="O24" s="19"/>
+      <c r="P24" s="19"/>
+      <c r="Q24" s="26"/>
+    </row>
+    <row r="25" spans="2:17" s="15" customFormat="1" ht="24.75" customHeight="1">
+      <c r="B25" s="30"/>
+      <c r="C25" s="31"/>
+      <c r="D25" s="31"/>
+      <c r="E25" s="31"/>
+      <c r="F25" s="31"/>
+      <c r="G25" s="31"/>
+      <c r="H25" s="19"/>
+      <c r="I25" s="19"/>
+      <c r="J25" s="19"/>
+      <c r="K25" s="19"/>
+      <c r="L25" s="19"/>
+      <c r="M25" s="19"/>
+      <c r="N25" s="19"/>
+      <c r="O25" s="19"/>
+      <c r="P25" s="19"/>
+      <c r="Q25" s="26"/>
+    </row>
+    <row r="26" spans="2:17" s="15" customFormat="1" ht="24.75" customHeight="1">
+      <c r="B26" s="30"/>
+      <c r="C26" s="31"/>
+      <c r="D26" s="31"/>
+      <c r="E26" s="31"/>
+      <c r="F26" s="31"/>
+      <c r="G26" s="31"/>
+      <c r="H26" s="19"/>
+      <c r="I26" s="19"/>
+      <c r="J26" s="19"/>
+      <c r="K26" s="19"/>
+      <c r="L26" s="19"/>
+      <c r="M26" s="19"/>
+      <c r="N26" s="19"/>
+      <c r="O26" s="19"/>
+      <c r="P26" s="19"/>
+      <c r="Q26" s="26"/>
+    </row>
+    <row r="27" spans="2:17" s="18" customFormat="1" ht="30.75" customHeight="1" thickBot="1">
+      <c r="B27" s="45"/>
+      <c r="C27" s="45"/>
+      <c r="D27" s="45"/>
+      <c r="E27" s="45"/>
+      <c r="F27" s="45"/>
+      <c r="G27" s="45"/>
+      <c r="H27" s="45"/>
+      <c r="I27" s="45"/>
+      <c r="J27" s="45"/>
+      <c r="K27" s="45"/>
+      <c r="L27" s="45"/>
+      <c r="M27" s="45"/>
+      <c r="N27" s="45"/>
+      <c r="O27" s="45"/>
+      <c r="P27" s="45"/>
+      <c r="Q27" s="19"/>
+    </row>
+    <row r="28" spans="2:17" s="15" customFormat="1" ht="30.75" customHeight="1">
+      <c r="B28" s="46" t="s">
+        <v>51</v>
+      </c>
+      <c r="C28" s="46"/>
+      <c r="D28" s="47"/>
+      <c r="E28" s="48"/>
+      <c r="F28" s="46" t="s">
+        <v>53</v>
+      </c>
+      <c r="G28" s="46"/>
+      <c r="H28" s="47"/>
+      <c r="I28" s="48"/>
+      <c r="J28" s="46" t="s">
         <v>54</v>
       </c>
-      <c r="I8" s="36" t="s">
-        <v>53</v>
-      </c>
-      <c r="J8" s="36" t="s">
-        <v>30</v>
-      </c>
-      <c r="K8" s="36" t="s">
-        <v>31</v>
-      </c>
-      <c r="L8" s="36" t="s">
-        <v>29</v>
-      </c>
-      <c r="M8" s="36" t="s">
-        <v>32</v>
-      </c>
-      <c r="N8" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="O8" s="30" t="s">
-        <v>33</v>
-      </c>
-      <c r="P8" s="19"/>
-      <c r="Q8" s="19"/>
-    </row>
-    <row r="9" spans="1:17" s="18" customFormat="1" ht="72" customHeight="1">
-      <c r="A9" s="18" t="s">
-        <v>39</v>
-      </c>
-      <c r="B9" s="37"/>
-      <c r="C9" s="37"/>
-      <c r="D9" s="37"/>
-      <c r="E9" s="37"/>
-      <c r="F9" s="37"/>
-      <c r="G9" s="37"/>
-      <c r="H9" s="37"/>
-      <c r="I9" s="37"/>
-      <c r="J9" s="37"/>
-      <c r="K9" s="37"/>
-      <c r="L9" s="37"/>
-      <c r="M9" s="37"/>
-      <c r="N9" s="31" t="s">
-        <v>26</v>
-      </c>
-      <c r="O9" s="30" t="s">
-        <v>51</v>
-      </c>
-      <c r="P9" s="19"/>
-      <c r="Q9" s="19"/>
-    </row>
-    <row r="10" spans="1:17" s="18" customFormat="1" ht="28.5" customHeight="1">
-      <c r="B10" s="16"/>
-      <c r="C10" s="16"/>
-      <c r="D10" s="16"/>
-      <c r="E10" s="16"/>
-      <c r="F10" s="16"/>
-      <c r="G10" s="16"/>
-      <c r="H10" s="50"/>
-      <c r="I10" s="50"/>
-      <c r="J10" s="50"/>
-      <c r="K10" s="50"/>
-      <c r="L10" s="50"/>
-      <c r="M10" s="50"/>
-      <c r="N10" s="50"/>
-      <c r="O10" s="50"/>
-      <c r="P10" s="50"/>
-      <c r="Q10" s="53"/>
-    </row>
-    <row r="11" spans="1:17" s="21" customFormat="1" ht="55.5" customHeight="1">
-      <c r="A11" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="B11" s="28" t="s">
-        <v>19</v>
-      </c>
-      <c r="C11" s="28" t="s">
-        <v>20</v>
-      </c>
-      <c r="D11" s="28" t="s">
-        <v>21</v>
-      </c>
-      <c r="E11" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="F11" s="28" t="s">
-        <v>23</v>
-      </c>
-      <c r="G11" s="29" t="s">
-        <v>24</v>
-      </c>
-      <c r="H11" s="52"/>
-      <c r="I11" s="52"/>
-      <c r="J11" s="52"/>
-      <c r="K11" s="52"/>
-      <c r="L11" s="52"/>
-      <c r="M11" s="52"/>
-      <c r="N11" s="52"/>
-      <c r="O11" s="52"/>
-      <c r="P11" s="52"/>
-      <c r="Q11" s="54"/>
-    </row>
-    <row r="12" spans="1:17" s="18" customFormat="1" ht="56.25" customHeight="1">
-      <c r="A12" s="18" t="s">
-        <v>40</v>
-      </c>
-      <c r="B12" s="32" t="s">
-        <v>34</v>
-      </c>
-      <c r="C12" s="32" t="s">
-        <v>36</v>
-      </c>
-      <c r="D12" s="32" t="s">
+      <c r="K28" s="46"/>
+      <c r="L28" s="47"/>
+      <c r="M28" s="48"/>
+      <c r="N28" s="48"/>
+      <c r="O28" s="46" t="s">
+        <v>55</v>
+      </c>
+      <c r="P28" s="46"/>
+      <c r="Q28" s="1"/>
+    </row>
+    <row r="29" spans="2:17" s="18" customFormat="1" ht="40.5">
+      <c r="B29" s="49" t="s">
         <v>52</v>
       </c>
-      <c r="E12" s="32" t="s">
-        <v>35</v>
-      </c>
-      <c r="F12" s="32" t="s">
-        <v>37</v>
-      </c>
-      <c r="G12" s="32" t="s">
-        <v>55</v>
-      </c>
-      <c r="H12" s="52"/>
-      <c r="I12" s="52"/>
-      <c r="J12" s="52"/>
-      <c r="K12" s="52"/>
-      <c r="L12" s="52"/>
-      <c r="M12" s="52"/>
-      <c r="N12" s="52"/>
-      <c r="O12" s="52"/>
-      <c r="P12" s="52"/>
-      <c r="Q12" s="54"/>
-    </row>
-    <row r="13" spans="1:17" s="18" customFormat="1" ht="36.75" customHeight="1">
-      <c r="B13" s="35"/>
-      <c r="C13" s="35"/>
-      <c r="D13" s="35"/>
-      <c r="E13" s="35"/>
-      <c r="F13" s="35"/>
-      <c r="G13" s="35"/>
-      <c r="H13" s="52"/>
-      <c r="I13" s="52"/>
-      <c r="J13" s="52"/>
-      <c r="K13" s="52"/>
-      <c r="L13" s="52"/>
-      <c r="M13" s="52"/>
-      <c r="N13" s="52"/>
-      <c r="O13" s="52"/>
-      <c r="P13" s="52"/>
-      <c r="Q13" s="54"/>
-    </row>
-    <row r="14" spans="1:17" s="18" customFormat="1" ht="30.75" customHeight="1">
-      <c r="B14" s="35"/>
-      <c r="C14" s="35"/>
-      <c r="D14" s="35"/>
-      <c r="E14" s="35"/>
-      <c r="F14" s="35"/>
-      <c r="G14" s="35"/>
-      <c r="H14" s="52"/>
-      <c r="I14" s="52"/>
-      <c r="J14" s="52"/>
-      <c r="K14" s="52"/>
-      <c r="L14" s="52"/>
-      <c r="M14" s="52"/>
-      <c r="N14" s="52"/>
-      <c r="O14" s="52"/>
-      <c r="P14" s="52"/>
-      <c r="Q14" s="54"/>
-    </row>
-    <row r="15" spans="1:17" s="18" customFormat="1" ht="24.95" customHeight="1">
-      <c r="B15" s="35"/>
-      <c r="C15" s="35"/>
-      <c r="D15" s="35"/>
-      <c r="E15" s="35"/>
-      <c r="F15" s="35"/>
-      <c r="G15" s="35"/>
-      <c r="H15" s="52"/>
-      <c r="I15" s="52"/>
-      <c r="J15" s="52"/>
-      <c r="K15" s="52"/>
-      <c r="L15" s="52"/>
-      <c r="M15" s="52"/>
-      <c r="N15" s="52"/>
-      <c r="O15" s="52"/>
-      <c r="P15" s="52"/>
-      <c r="Q15" s="54"/>
-    </row>
-    <row r="16" spans="1:17" s="18" customFormat="1" ht="24.95" customHeight="1">
-      <c r="B16" s="35"/>
-      <c r="C16" s="35"/>
-      <c r="D16" s="35"/>
-      <c r="E16" s="35"/>
-      <c r="F16" s="35"/>
-      <c r="G16" s="35"/>
-      <c r="H16" s="52"/>
-      <c r="I16" s="52"/>
-      <c r="J16" s="52"/>
-      <c r="K16" s="52"/>
-      <c r="L16" s="52"/>
-      <c r="M16" s="52"/>
-      <c r="N16" s="52"/>
-      <c r="O16" s="52"/>
-      <c r="P16" s="52"/>
-      <c r="Q16" s="54"/>
-    </row>
-    <row r="17" spans="2:17" s="18" customFormat="1" ht="24.95" customHeight="1">
-      <c r="B17" s="35"/>
-      <c r="C17" s="35"/>
-      <c r="D17" s="35"/>
-      <c r="E17" s="35"/>
-      <c r="F17" s="35"/>
-      <c r="G17" s="35"/>
-      <c r="H17" s="52"/>
-      <c r="I17" s="52"/>
-      <c r="J17" s="52"/>
-      <c r="K17" s="52"/>
-      <c r="L17" s="52"/>
-      <c r="M17" s="52"/>
-      <c r="N17" s="52"/>
-      <c r="O17" s="52"/>
-      <c r="P17" s="52"/>
-      <c r="Q17" s="54"/>
-    </row>
-    <row r="18" spans="2:17" s="18" customFormat="1" ht="24.95" customHeight="1">
-      <c r="B18" s="35"/>
-      <c r="C18" s="35"/>
-      <c r="D18" s="35"/>
-      <c r="E18" s="35"/>
-      <c r="F18" s="35"/>
-      <c r="G18" s="35"/>
-      <c r="H18" s="52"/>
-      <c r="I18" s="52"/>
-      <c r="J18" s="52"/>
-      <c r="K18" s="52"/>
-      <c r="L18" s="52"/>
-      <c r="M18" s="52"/>
-      <c r="N18" s="52"/>
-      <c r="O18" s="52"/>
-      <c r="P18" s="52"/>
-      <c r="Q18" s="54"/>
-    </row>
-    <row r="19" spans="2:17" s="18" customFormat="1" ht="24.95" customHeight="1">
-      <c r="B19" s="35"/>
-      <c r="C19" s="35"/>
-      <c r="D19" s="35"/>
-      <c r="E19" s="35"/>
-      <c r="F19" s="35"/>
-      <c r="G19" s="35"/>
-      <c r="H19" s="52"/>
-      <c r="I19" s="52"/>
-      <c r="J19" s="52"/>
-      <c r="K19" s="52"/>
-      <c r="L19" s="52"/>
-      <c r="M19" s="52"/>
-      <c r="N19" s="52"/>
-      <c r="O19" s="52"/>
-      <c r="P19" s="52"/>
-      <c r="Q19" s="54"/>
-    </row>
-    <row r="20" spans="2:17" s="18" customFormat="1" ht="24.75" customHeight="1">
-      <c r="B20" s="49"/>
-      <c r="C20" s="50"/>
-      <c r="D20" s="50"/>
-      <c r="E20" s="50"/>
-      <c r="F20" s="50"/>
-      <c r="G20" s="50"/>
-      <c r="H20" s="52"/>
-      <c r="I20" s="52"/>
-      <c r="J20" s="52"/>
-      <c r="K20" s="52"/>
-      <c r="L20" s="52"/>
-      <c r="M20" s="52"/>
-      <c r="N20" s="52"/>
-      <c r="O20" s="52"/>
-      <c r="P20" s="52"/>
-      <c r="Q20" s="54"/>
-    </row>
-    <row r="21" spans="2:17" s="18" customFormat="1" ht="24.75" customHeight="1">
-      <c r="B21" s="51"/>
-      <c r="C21" s="52"/>
-      <c r="D21" s="52"/>
-      <c r="E21" s="52"/>
-      <c r="F21" s="52"/>
-      <c r="G21" s="52"/>
-      <c r="H21" s="33"/>
-      <c r="I21" s="33"/>
-      <c r="J21" s="33"/>
-      <c r="K21" s="33"/>
-      <c r="L21" s="33"/>
-      <c r="M21" s="33"/>
-      <c r="N21" s="33"/>
-      <c r="O21" s="33"/>
-      <c r="P21" s="33"/>
-      <c r="Q21" s="34"/>
-    </row>
-    <row r="22" spans="2:17" s="18" customFormat="1" ht="24.75" customHeight="1">
-      <c r="B22" s="51"/>
-      <c r="C22" s="52"/>
-      <c r="D22" s="52"/>
-      <c r="E22" s="52"/>
-      <c r="F22" s="52"/>
-      <c r="G22" s="52"/>
-      <c r="H22" s="33"/>
-      <c r="I22" s="33"/>
-      <c r="J22" s="33"/>
-      <c r="K22" s="33"/>
-      <c r="L22" s="33"/>
-      <c r="M22" s="33"/>
-      <c r="N22" s="33"/>
-      <c r="O22" s="33"/>
-      <c r="P22" s="33"/>
-      <c r="Q22" s="34"/>
-    </row>
-    <row r="23" spans="2:17" s="18" customFormat="1" ht="24.75" customHeight="1">
-      <c r="B23" s="51"/>
-      <c r="C23" s="52"/>
-      <c r="D23" s="52"/>
-      <c r="E23" s="52"/>
-      <c r="F23" s="52"/>
-      <c r="G23" s="52"/>
-      <c r="H23" s="33"/>
-      <c r="I23" s="33"/>
-      <c r="J23" s="33"/>
-      <c r="K23" s="33"/>
-      <c r="L23" s="33"/>
-      <c r="M23" s="33"/>
-      <c r="N23" s="33"/>
-      <c r="O23" s="33"/>
-      <c r="P23" s="33"/>
-      <c r="Q23" s="34"/>
-    </row>
-    <row r="24" spans="2:17" s="18" customFormat="1" ht="24.75" customHeight="1">
-      <c r="B24" s="51"/>
-      <c r="C24" s="52"/>
-      <c r="D24" s="52"/>
-      <c r="E24" s="52"/>
-      <c r="F24" s="52"/>
-      <c r="G24" s="52"/>
-      <c r="H24" s="33"/>
-      <c r="I24" s="33"/>
-      <c r="J24" s="33"/>
-      <c r="K24" s="33"/>
-      <c r="L24" s="33"/>
-      <c r="M24" s="33"/>
-      <c r="N24" s="33"/>
-      <c r="O24" s="33"/>
-      <c r="P24" s="33"/>
-      <c r="Q24" s="34"/>
-    </row>
-    <row r="25" spans="2:17" s="18" customFormat="1" ht="24.75" customHeight="1">
-      <c r="B25" s="51"/>
-      <c r="C25" s="52"/>
-      <c r="D25" s="52"/>
-      <c r="E25" s="52"/>
-      <c r="F25" s="52"/>
-      <c r="G25" s="52"/>
-      <c r="H25" s="33"/>
-      <c r="I25" s="33"/>
-      <c r="J25" s="33"/>
-      <c r="K25" s="33"/>
-      <c r="L25" s="33"/>
-      <c r="M25" s="33"/>
-      <c r="N25" s="33"/>
-      <c r="O25" s="33"/>
-      <c r="P25" s="33"/>
-      <c r="Q25" s="34"/>
-    </row>
-    <row r="26" spans="2:17" s="18" customFormat="1" ht="24.75" customHeight="1">
-      <c r="B26" s="51"/>
-      <c r="C26" s="52"/>
-      <c r="D26" s="52"/>
-      <c r="E26" s="52"/>
-      <c r="F26" s="52"/>
-      <c r="G26" s="52"/>
-      <c r="H26" s="33"/>
-      <c r="I26" s="33"/>
-      <c r="J26" s="33"/>
-      <c r="K26" s="33"/>
-      <c r="L26" s="33"/>
-      <c r="M26" s="33"/>
-      <c r="N26" s="33"/>
-      <c r="O26" s="33"/>
-      <c r="P26" s="33"/>
-      <c r="Q26" s="34"/>
-    </row>
-    <row r="27" spans="2:17" s="18" customFormat="1" ht="24.95" customHeight="1">
-      <c r="B27" s="51"/>
-      <c r="C27" s="52"/>
-      <c r="D27" s="52"/>
-      <c r="E27" s="52"/>
-      <c r="F27" s="52"/>
-      <c r="G27" s="52"/>
-      <c r="H27" s="16"/>
-      <c r="I27" s="16"/>
-      <c r="J27" s="16"/>
-      <c r="K27" s="16"/>
-      <c r="L27" s="16"/>
-      <c r="M27" s="16"/>
-      <c r="N27" s="16"/>
-      <c r="O27" s="16"/>
-      <c r="P27" s="16"/>
-      <c r="Q27" s="25"/>
-    </row>
-    <row r="28" spans="2:17" s="22" customFormat="1" ht="38.25" customHeight="1">
-      <c r="B28" s="55" t="s">
-        <v>43</v>
-      </c>
-      <c r="C28" s="60"/>
-      <c r="D28" s="57" t="s">
-        <v>44</v>
-      </c>
-      <c r="E28" s="58"/>
-      <c r="F28" s="58"/>
-      <c r="G28" s="59"/>
-      <c r="H28" s="55" t="s">
-        <v>45</v>
-      </c>
-      <c r="I28" s="56"/>
-      <c r="J28" s="26"/>
-      <c r="K28" s="27"/>
-      <c r="L28" s="55" t="s">
-        <v>46</v>
-      </c>
-      <c r="M28" s="56"/>
-      <c r="N28" s="56"/>
-      <c r="O28" s="56"/>
-      <c r="P28" s="60"/>
-      <c r="Q28" s="61" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="29" spans="2:17" s="22" customFormat="1">
-      <c r="B29" s="23"/>
-      <c r="C29" s="23"/>
-      <c r="D29" s="23"/>
-      <c r="E29" s="23"/>
-      <c r="F29" s="23"/>
-      <c r="G29" s="23"/>
-      <c r="H29" s="23"/>
-      <c r="I29" s="23"/>
-      <c r="J29" s="23"/>
-      <c r="K29" s="23"/>
-      <c r="L29" s="23"/>
-      <c r="M29" s="23"/>
-      <c r="N29" s="23"/>
-      <c r="O29" s="23"/>
-      <c r="P29" s="23"/>
-      <c r="Q29" s="23"/>
-    </row>
-    <row r="30" spans="2:17" s="22" customFormat="1">
-      <c r="B30" s="23"/>
-      <c r="C30" s="23"/>
-      <c r="D30" s="23"/>
-      <c r="E30" s="23"/>
-      <c r="F30" s="23"/>
-      <c r="G30" s="23"/>
-      <c r="H30" s="23"/>
-      <c r="I30" s="23"/>
-      <c r="J30" s="23"/>
-      <c r="K30" s="23"/>
-      <c r="L30" s="23"/>
-      <c r="M30" s="23"/>
-      <c r="N30" s="23"/>
-      <c r="O30" s="23"/>
-      <c r="P30" s="23"/>
-      <c r="Q30" s="23"/>
-    </row>
-    <row r="31" spans="2:17" s="22" customFormat="1">
-      <c r="B31" s="23"/>
-      <c r="C31" s="23"/>
-      <c r="D31" s="23"/>
-      <c r="E31" s="23"/>
-      <c r="F31" s="23"/>
-      <c r="G31" s="23"/>
-      <c r="H31" s="23"/>
-      <c r="I31" s="23"/>
-      <c r="J31" s="23"/>
-      <c r="K31" s="23"/>
-      <c r="L31" s="23"/>
-      <c r="M31" s="23"/>
-      <c r="N31" s="23"/>
-      <c r="O31" s="23"/>
-      <c r="P31" s="23"/>
-      <c r="Q31" s="23"/>
-    </row>
-    <row r="32" spans="2:17" s="22" customFormat="1">
-      <c r="B32" s="23"/>
-      <c r="C32" s="23"/>
-      <c r="D32" s="23"/>
-      <c r="E32" s="23"/>
-      <c r="F32" s="23"/>
-      <c r="G32" s="23"/>
-      <c r="H32" s="23"/>
-      <c r="I32" s="23"/>
-      <c r="J32" s="23"/>
-      <c r="K32" s="23"/>
-      <c r="L32" s="23"/>
-      <c r="M32" s="23"/>
-      <c r="N32" s="23"/>
-      <c r="O32" s="23"/>
-      <c r="P32" s="23"/>
-      <c r="Q32" s="23"/>
-    </row>
-    <row r="33" spans="2:17" s="22" customFormat="1">
-      <c r="B33" s="23"/>
-      <c r="C33" s="23"/>
-      <c r="D33" s="23"/>
-      <c r="E33" s="23"/>
-      <c r="F33" s="23"/>
-      <c r="G33" s="23"/>
-      <c r="H33" s="23"/>
-      <c r="I33" s="23"/>
-      <c r="J33" s="23"/>
-      <c r="K33" s="23"/>
-      <c r="L33" s="23"/>
-      <c r="M33" s="23"/>
-      <c r="N33" s="23"/>
-      <c r="O33" s="23"/>
-      <c r="P33" s="23"/>
-      <c r="Q33" s="23"/>
-    </row>
-    <row r="34" spans="2:17" s="22" customFormat="1">
-      <c r="B34" s="23"/>
-      <c r="C34" s="23"/>
-      <c r="D34" s="23"/>
-      <c r="E34" s="23"/>
-      <c r="F34" s="23"/>
-      <c r="G34" s="23"/>
-      <c r="H34" s="23"/>
-      <c r="I34" s="23"/>
-      <c r="J34" s="23"/>
-      <c r="K34" s="23"/>
-      <c r="L34" s="23"/>
-      <c r="M34" s="23"/>
-      <c r="N34" s="23"/>
-      <c r="O34" s="23"/>
-      <c r="P34" s="23"/>
-      <c r="Q34" s="23"/>
-    </row>
-    <row r="35" spans="2:17" s="22" customFormat="1">
-      <c r="B35" s="23"/>
-      <c r="C35" s="23"/>
-      <c r="D35" s="23"/>
-      <c r="E35" s="23"/>
-      <c r="F35" s="23"/>
-      <c r="G35" s="23"/>
-      <c r="H35" s="23"/>
-      <c r="I35" s="23"/>
-      <c r="J35" s="23"/>
-      <c r="K35" s="23"/>
-      <c r="L35" s="23"/>
-      <c r="M35" s="23"/>
-      <c r="N35" s="23"/>
-      <c r="O35" s="23"/>
-      <c r="P35" s="23"/>
-      <c r="Q35" s="23"/>
-    </row>
+      <c r="C29" s="49"/>
+      <c r="D29" s="50"/>
+      <c r="E29" s="51"/>
+      <c r="F29" s="52" t="s">
+        <v>56</v>
+      </c>
+      <c r="G29" s="52"/>
+      <c r="H29" s="50"/>
+      <c r="I29" s="51"/>
+      <c r="J29" s="52" t="s">
+        <v>57</v>
+      </c>
+      <c r="K29" s="52"/>
+      <c r="L29" s="50"/>
+      <c r="M29" s="51"/>
+      <c r="N29" s="51"/>
+      <c r="O29" s="51" t="s">
+        <v>58</v>
+      </c>
+      <c r="P29" s="50"/>
+      <c r="Q29" s="19"/>
+    </row>
+    <row r="30" spans="2:17" s="18" customFormat="1">
+      <c r="B30" s="19"/>
+      <c r="C30" s="19"/>
+      <c r="D30" s="19"/>
+      <c r="E30" s="19"/>
+      <c r="F30" s="19"/>
+      <c r="G30" s="19"/>
+      <c r="H30" s="19"/>
+      <c r="I30" s="19"/>
+      <c r="J30" s="19"/>
+      <c r="K30" s="19"/>
+      <c r="L30" s="19"/>
+      <c r="M30" s="19"/>
+      <c r="N30" s="19"/>
+      <c r="O30" s="19"/>
+      <c r="P30" s="19"/>
+      <c r="Q30" s="19"/>
+    </row>
+    <row r="33" ht="31.5" customHeight="1"/>
   </sheetData>
   <mergeCells count="36">
-    <mergeCell ref="B20:G27"/>
-    <mergeCell ref="H10:Q20"/>
-    <mergeCell ref="H28:I28"/>
-    <mergeCell ref="D28:G28"/>
-    <mergeCell ref="L28:P28"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="O28:P28"/>
     <mergeCell ref="B28:C28"/>
+    <mergeCell ref="G8:G9"/>
+    <mergeCell ref="E8:E9"/>
+    <mergeCell ref="L8:L9"/>
+    <mergeCell ref="J8:J9"/>
+    <mergeCell ref="F8:F9"/>
+    <mergeCell ref="O4:Q4"/>
+    <mergeCell ref="P6:P7"/>
+    <mergeCell ref="H8:H9"/>
+    <mergeCell ref="Q6:Q7"/>
+    <mergeCell ref="N6:N7"/>
+    <mergeCell ref="O6:O7"/>
+    <mergeCell ref="M8:M9"/>
+    <mergeCell ref="K8:K9"/>
+    <mergeCell ref="I8:I9"/>
     <mergeCell ref="B8:B9"/>
     <mergeCell ref="C8:C9"/>
     <mergeCell ref="J1:O2"/>
@@ -1944,20 +1846,8 @@
     <mergeCell ref="M6:M7"/>
     <mergeCell ref="B6:B7"/>
     <mergeCell ref="D8:D9"/>
-    <mergeCell ref="O4:Q4"/>
-    <mergeCell ref="P6:P7"/>
-    <mergeCell ref="H8:H9"/>
-    <mergeCell ref="Q6:Q7"/>
-    <mergeCell ref="N6:N7"/>
-    <mergeCell ref="O6:O7"/>
-    <mergeCell ref="M8:M9"/>
-    <mergeCell ref="K8:K9"/>
-    <mergeCell ref="I8:I9"/>
-    <mergeCell ref="G8:G9"/>
-    <mergeCell ref="E8:E9"/>
-    <mergeCell ref="L8:L9"/>
-    <mergeCell ref="J8:J9"/>
-    <mergeCell ref="F8:F9"/>
+    <mergeCell ref="B20:G26"/>
+    <mergeCell ref="H10:Q20"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.25" top="0.25" bottom="0.5" header="0" footer="0"/>
   <pageSetup paperSize="9" scale="52" fitToHeight="0" orientation="landscape" r:id="rId1"/>

--- a/APLOS/POPResources/Templates/MlrBengali20181.xlsx
+++ b/APLOS/POPResources/Templates/MlrBengali20181.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26327"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\AplosProject\APLOS\POPResources\Templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFEC9B3C-66B3-488A-9C37-52D56BF3CA82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41D870E4-8DF3-4822-A41C-3A9631AB26FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="59">
   <si>
     <t xml:space="preserve">কার্ড নং </t>
   </si>
@@ -51,9 +51,6 @@
     <t xml:space="preserve">২০০৬ সালের শ্রম আইনের ৪৭ ধারার ০১ উপধারা এর অধিনে প্রদত্ত শয্যাগত হওয়ার নোটিশের তারিখ </t>
   </si>
   <si>
-    <t xml:space="preserve">২০০৬ সালের শ্রম আইনের ৪৮ ধারার অধীনে প্রদত্ত শয্যাগত হওয়ার নোটিশের তারিখের  পূর্ববর্তী তিন মাসে মোট কতদিন কাজ করেছেন এবং কত টাকা আয় করেছেন </t>
-  </si>
-  <si>
     <t>২০০৬ সালের শ্রম আইনের ৪৮ অনুযায়ী হিসাবকৃত দৈনিক গড় মজুরী (টাকা)</t>
   </si>
   <si>
@@ -87,9 +84,6 @@
     <t>প্রাপ্ত মোট মাসিক মজুরী</t>
   </si>
   <si>
-    <t>উৎসব বোনাস</t>
-  </si>
-  <si>
     <t>সর্বমোট প্রাপ্ত মজুরী</t>
   </si>
   <si>
@@ -129,9 +123,6 @@
     <t>{StructureAmount}</t>
   </si>
   <si>
-    <t>{BonusAmount}</t>
-  </si>
-  <si>
     <t>RefRow</t>
   </si>
   <si>
@@ -207,7 +198,10 @@
     <t>১৩৫-১৩৮, (২য়-৫ম তলা ) আবদুল্লাহপুর, উত্তরা, ঢাকা-১২৩০</t>
   </si>
   <si>
-    <t>(বাংলাদেশ শ্রম আইন ২০০৬ এবং সংশোধিত ২০১৮ এর ধারা আনুযায়ী)</t>
+    <t>(বাংলাদেশ শ্রম আইন ২০০৬ এবং সংশোধিত ২০২২ এর ধারা আনুযায়ী)</t>
+  </si>
+  <si>
+    <t>(বাংলাদেশ শ্রম আইন ২০০৬ এবং নতুন সংশোধিত ২০২২ এর ধারা ৪৮ (২) অনুযায়ী প্রসূতিকল্যান সুবিধা হিসাব করিবার ক্ষেত্রে শ্রমিকের সর্বশেষ মাসিক প্রাপ্ত মোট মজুরীকে ২৬ দ্বারা ভাগ করিয়া ০১ দিনের গড় মজুরী নির্ধারন করিতে হইবে। দৈনিক গড় মজুরী (টাকা)</t>
   </si>
 </sst>
 </file>
@@ -218,7 +212,7 @@
     <numFmt numFmtId="164" formatCode="[$-5000445]###0;"/>
     <numFmt numFmtId="165" formatCode="[$-5000445]###0.0;"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="14">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -284,6 +278,19 @@
       <color theme="1"/>
       <name val="RinkiyMJ"/>
     </font>
+    <font>
+      <b/>
+      <sz val="20"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="20"/>
+      <color theme="1"/>
+      <name val="SutonnyMJ"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -473,7 +480,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -543,6 +550,69 @@
     <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -552,72 +622,19 @@
     <xf numFmtId="165" fontId="7" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -980,7 +997,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q32"/>
+  <dimension ref="A1:Q29"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="37" style="4" hidden="1" customWidth="1"/>
@@ -1007,17 +1024,19 @@
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
-      <c r="G1" s="25" t="s">
-        <v>58</v>
-      </c>
-      <c r="H1" s="25"/>
-      <c r="I1" s="25"/>
-      <c r="J1" s="25"/>
-      <c r="K1" s="25"/>
-      <c r="L1" s="25"/>
-      <c r="M1" s="25"/>
+      <c r="G1" s="46" t="s">
+        <v>55</v>
+      </c>
+      <c r="H1" s="46"/>
+      <c r="I1" s="46"/>
+      <c r="J1" s="46"/>
+      <c r="K1" s="46"/>
+      <c r="L1" s="46"/>
+      <c r="M1" s="46"/>
       <c r="N1" s="1"/>
-      <c r="O1" s="1"/>
+      <c r="O1" s="51"/>
+      <c r="P1" s="52"/>
+      <c r="Q1" s="52"/>
     </row>
     <row r="2" spans="1:17" ht="46.5" customHeight="1">
       <c r="B2" s="5"/>
@@ -1025,199 +1044,198 @@
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
-      <c r="H2" s="26" t="s">
-        <v>59</v>
-      </c>
-      <c r="I2" s="26"/>
-      <c r="J2" s="26"/>
-      <c r="K2" s="26"/>
-      <c r="L2" s="26"/>
-      <c r="M2" s="26"/>
+      <c r="H2" s="47" t="s">
+        <v>56</v>
+      </c>
+      <c r="I2" s="47"/>
+      <c r="J2" s="47"/>
+      <c r="K2" s="47"/>
+      <c r="L2" s="47"/>
+      <c r="M2" s="47"/>
       <c r="N2" s="1"/>
       <c r="O2" s="1"/>
     </row>
     <row r="3" spans="1:17" s="6" customFormat="1" ht="50.25" customHeight="1">
-      <c r="A3" s="50"/>
-      <c r="B3" s="48" t="s">
+      <c r="B3" s="49" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="51"/>
-      <c r="D3" s="51"/>
-      <c r="E3" s="51"/>
-      <c r="F3" s="51"/>
-      <c r="G3" s="51"/>
-      <c r="H3" s="51"/>
-      <c r="I3" s="51"/>
-      <c r="J3" s="51"/>
-      <c r="K3" s="51"/>
-      <c r="L3" s="51"/>
-      <c r="M3" s="51"/>
-      <c r="N3" s="51"/>
-      <c r="O3" s="51"/>
-      <c r="P3" s="51"/>
-      <c r="Q3" s="51"/>
+      <c r="C3" s="50"/>
+      <c r="D3" s="50"/>
+      <c r="E3" s="50"/>
+      <c r="F3" s="50"/>
+      <c r="G3" s="50"/>
+      <c r="H3" s="50"/>
+      <c r="I3" s="50"/>
+      <c r="J3" s="50"/>
+      <c r="K3" s="50"/>
+      <c r="L3" s="50"/>
+      <c r="M3" s="50"/>
+      <c r="N3" s="50"/>
+      <c r="O3" s="50"/>
+      <c r="P3" s="50"/>
+      <c r="Q3" s="50"/>
     </row>
     <row r="4" spans="1:17" s="6" customFormat="1" ht="48.75" customHeight="1">
-      <c r="A4" s="49"/>
-      <c r="B4" s="45" t="s">
-        <v>60</v>
-      </c>
-      <c r="C4" s="45"/>
-      <c r="D4" s="45"/>
-      <c r="E4" s="45"/>
-      <c r="F4" s="45"/>
-      <c r="G4" s="45"/>
-      <c r="H4" s="45"/>
-      <c r="I4" s="45"/>
-      <c r="J4" s="45"/>
-      <c r="K4" s="45"/>
-      <c r="L4" s="45"/>
-      <c r="M4" s="45"/>
-      <c r="N4" s="45"/>
-      <c r="O4" s="45"/>
-      <c r="P4" s="45"/>
-      <c r="Q4" s="45"/>
+      <c r="A4"/>
+      <c r="B4" s="53" t="s">
+        <v>57</v>
+      </c>
+      <c r="C4" s="53"/>
+      <c r="D4" s="53"/>
+      <c r="E4" s="53"/>
+      <c r="F4" s="53"/>
+      <c r="G4" s="53"/>
+      <c r="H4" s="53"/>
+      <c r="I4" s="53"/>
+      <c r="J4" s="53"/>
+      <c r="K4" s="53"/>
+      <c r="L4" s="53"/>
+      <c r="M4" s="53"/>
+      <c r="N4" s="53"/>
+      <c r="O4" s="53"/>
+      <c r="P4" s="53"/>
+      <c r="Q4" s="53"/>
     </row>
     <row r="5" spans="1:17" s="7" customFormat="1" ht="251.25" customHeight="1">
-      <c r="B5" s="36" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5" s="36" t="s">
+      <c r="B5" s="35" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" s="35" t="s">
         <v>1</v>
       </c>
-      <c r="D5" s="36" t="s">
+      <c r="D5" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="E5" s="36" t="s">
+      <c r="E5" s="35" t="s">
         <v>4</v>
       </c>
-      <c r="F5" s="36" t="s">
+      <c r="F5" s="35" t="s">
         <v>5</v>
       </c>
-      <c r="G5" s="36" t="s">
+      <c r="G5" s="35" t="s">
         <v>6</v>
       </c>
-      <c r="H5" s="36" t="s">
+      <c r="H5" s="35" t="s">
         <v>7</v>
       </c>
-      <c r="I5" s="46" t="s">
+      <c r="I5" s="33" t="s">
+        <v>58</v>
+      </c>
+      <c r="J5" s="34"/>
+      <c r="K5" s="35" t="s">
         <v>8</v>
       </c>
-      <c r="J5" s="47"/>
-      <c r="K5" s="36" t="s">
+      <c r="L5" s="35" t="s">
+        <v>53</v>
+      </c>
+      <c r="M5" s="35" t="s">
+        <v>11</v>
+      </c>
+      <c r="N5" s="44" t="s">
         <v>9</v>
       </c>
-      <c r="L5" s="36" t="s">
-        <v>56</v>
-      </c>
-      <c r="M5" s="36" t="s">
+      <c r="O5" s="35" t="s">
+        <v>10</v>
+      </c>
+      <c r="P5" s="35" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q5" s="43" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" s="8" customFormat="1" ht="93">
+      <c r="B6" s="36"/>
+      <c r="C6" s="36"/>
+      <c r="D6" s="36"/>
+      <c r="E6" s="36"/>
+      <c r="F6" s="36"/>
+      <c r="G6" s="36"/>
+      <c r="H6" s="36"/>
+      <c r="I6" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="N5" s="39" t="s">
-        <v>10</v>
-      </c>
-      <c r="O5" s="36" t="s">
-        <v>11</v>
-      </c>
-      <c r="P5" s="36" t="s">
-        <v>57</v>
-      </c>
-      <c r="Q5" s="38" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17" s="8" customFormat="1" ht="93">
-      <c r="B6" s="37"/>
-      <c r="C6" s="37"/>
-      <c r="D6" s="37"/>
-      <c r="E6" s="37"/>
-      <c r="F6" s="37"/>
-      <c r="G6" s="37"/>
-      <c r="H6" s="37"/>
-      <c r="I6" s="15" t="s">
+      <c r="J6" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="J6" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="K6" s="37"/>
-      <c r="L6" s="37"/>
-      <c r="M6" s="37"/>
-      <c r="N6" s="40"/>
-      <c r="O6" s="37"/>
-      <c r="P6" s="37"/>
-      <c r="Q6" s="29"/>
+      <c r="K6" s="36"/>
+      <c r="L6" s="36"/>
+      <c r="M6" s="36"/>
+      <c r="N6" s="45"/>
+      <c r="O6" s="36"/>
+      <c r="P6" s="36"/>
+      <c r="Q6" s="42"/>
     </row>
     <row r="7" spans="1:17" s="8" customFormat="1" ht="120" customHeight="1">
       <c r="A7" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="B7" s="28" t="s">
+        <v>32</v>
+      </c>
+      <c r="B7" s="41" t="s">
+        <v>36</v>
+      </c>
+      <c r="C7" s="41" t="s">
+        <v>37</v>
+      </c>
+      <c r="D7" s="41" t="s">
+        <v>22</v>
+      </c>
+      <c r="E7" s="41" t="s">
         <v>39</v>
       </c>
-      <c r="C7" s="28" t="s">
-        <v>40</v>
-      </c>
-      <c r="D7" s="28" t="s">
+      <c r="F7" s="41" t="s">
+        <v>38</v>
+      </c>
+      <c r="G7" s="41" t="s">
+        <v>23</v>
+      </c>
+      <c r="H7" s="41" t="s">
+        <v>43</v>
+      </c>
+      <c r="I7" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="J7" s="41" t="s">
+        <v>25</v>
+      </c>
+      <c r="K7" s="41" t="s">
+        <v>26</v>
+      </c>
+      <c r="L7" s="41" t="s">
         <v>24</v>
       </c>
-      <c r="E7" s="28" t="s">
-        <v>42</v>
-      </c>
-      <c r="F7" s="28" t="s">
-        <v>41</v>
-      </c>
-      <c r="G7" s="28" t="s">
-        <v>25</v>
-      </c>
-      <c r="H7" s="28" t="s">
-        <v>46</v>
-      </c>
-      <c r="I7" s="28" t="s">
-        <v>45</v>
-      </c>
-      <c r="J7" s="28" t="s">
+      <c r="M7" s="41" t="s">
         <v>27</v>
       </c>
-      <c r="K7" s="28" t="s">
+      <c r="N7" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="O7" s="15" t="s">
         <v>28</v>
-      </c>
-      <c r="L7" s="28" t="s">
-        <v>26</v>
-      </c>
-      <c r="M7" s="28" t="s">
-        <v>29</v>
-      </c>
-      <c r="N7" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="O7" s="15" t="s">
-        <v>30</v>
       </c>
       <c r="P7" s="9"/>
       <c r="Q7" s="9"/>
     </row>
     <row r="8" spans="1:17" s="8" customFormat="1" ht="120" customHeight="1">
       <c r="A8" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="B8" s="29"/>
-      <c r="C8" s="29"/>
-      <c r="D8" s="29"/>
-      <c r="E8" s="29"/>
-      <c r="F8" s="29"/>
-      <c r="G8" s="29"/>
-      <c r="H8" s="29"/>
-      <c r="I8" s="29"/>
-      <c r="J8" s="29"/>
-      <c r="K8" s="29"/>
-      <c r="L8" s="29"/>
-      <c r="M8" s="29"/>
+        <v>33</v>
+      </c>
+      <c r="B8" s="42"/>
+      <c r="C8" s="42"/>
+      <c r="D8" s="42"/>
+      <c r="E8" s="42"/>
+      <c r="F8" s="42"/>
+      <c r="G8" s="42"/>
+      <c r="H8" s="42"/>
+      <c r="I8" s="42"/>
+      <c r="J8" s="42"/>
+      <c r="K8" s="42"/>
+      <c r="L8" s="42"/>
+      <c r="M8" s="42"/>
       <c r="N8" s="16" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="O8" s="15" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="P8" s="9"/>
       <c r="Q8" s="9"/>
@@ -1229,82 +1247,76 @@
       <c r="E9" s="1"/>
       <c r="F9" s="1"/>
       <c r="G9" s="1"/>
-      <c r="H9" s="31"/>
-      <c r="I9" s="31"/>
-      <c r="J9" s="31"/>
-      <c r="K9" s="31"/>
-      <c r="L9" s="31"/>
-      <c r="M9" s="31"/>
-      <c r="N9" s="31"/>
-      <c r="O9" s="31"/>
-      <c r="P9" s="31"/>
-      <c r="Q9" s="34"/>
+      <c r="H9" s="37"/>
+      <c r="I9" s="37"/>
+      <c r="J9" s="37"/>
+      <c r="K9" s="37"/>
+      <c r="L9" s="37"/>
+      <c r="M9" s="37"/>
+      <c r="N9" s="37"/>
+      <c r="O9" s="37"/>
+      <c r="P9" s="37"/>
+      <c r="Q9" s="38"/>
     </row>
     <row r="10" spans="1:17" s="11" customFormat="1" ht="55.5" customHeight="1">
       <c r="A10" s="10" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B10" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="C10" s="13" t="s">
+      <c r="D10" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="D10" s="13" t="s">
+      <c r="E10" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="E10" s="13" t="s">
+      <c r="F10" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="F10" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="G10" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="H10" s="33"/>
-      <c r="I10" s="33"/>
-      <c r="J10" s="33"/>
-      <c r="K10" s="33"/>
-      <c r="L10" s="33"/>
-      <c r="M10" s="33"/>
-      <c r="N10" s="33"/>
-      <c r="O10" s="33"/>
-      <c r="P10" s="33"/>
-      <c r="Q10" s="35"/>
+      <c r="H10" s="39"/>
+      <c r="I10" s="39"/>
+      <c r="J10" s="39"/>
+      <c r="K10" s="39"/>
+      <c r="L10" s="39"/>
+      <c r="M10" s="39"/>
+      <c r="N10" s="39"/>
+      <c r="O10" s="39"/>
+      <c r="P10" s="39"/>
+      <c r="Q10" s="40"/>
     </row>
     <row r="11" spans="1:17" s="8" customFormat="1" ht="56.25" customHeight="1">
       <c r="A11" s="8" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B11" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="C11" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="C11" s="17" t="s">
-        <v>33</v>
-      </c>
       <c r="D11" s="17" t="s">
+        <v>41</v>
+      </c>
+      <c r="E11" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="F11" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="E11" s="17" t="s">
-        <v>32</v>
-      </c>
-      <c r="F11" s="17" t="s">
-        <v>34</v>
-      </c>
-      <c r="G11" s="17" t="s">
-        <v>47</v>
-      </c>
-      <c r="H11" s="33"/>
-      <c r="I11" s="33"/>
-      <c r="J11" s="33"/>
-      <c r="K11" s="33"/>
-      <c r="L11" s="33"/>
-      <c r="M11" s="33"/>
-      <c r="N11" s="33"/>
-      <c r="O11" s="33"/>
-      <c r="P11" s="33"/>
-      <c r="Q11" s="35"/>
+      <c r="H11" s="39"/>
+      <c r="I11" s="39"/>
+      <c r="J11" s="39"/>
+      <c r="K11" s="39"/>
+      <c r="L11" s="39"/>
+      <c r="M11" s="39"/>
+      <c r="N11" s="39"/>
+      <c r="O11" s="39"/>
+      <c r="P11" s="39"/>
+      <c r="Q11" s="40"/>
     </row>
     <row r="12" spans="1:17" s="8" customFormat="1" ht="60" customHeight="1">
       <c r="B12" s="19"/>
@@ -1312,151 +1324,145 @@
       <c r="D12" s="19"/>
       <c r="E12" s="19"/>
       <c r="F12" s="19"/>
-      <c r="G12" s="19"/>
-      <c r="H12" s="33"/>
-      <c r="I12" s="33"/>
-      <c r="J12" s="33"/>
-      <c r="K12" s="33"/>
-      <c r="L12" s="33"/>
-      <c r="M12" s="33"/>
-      <c r="N12" s="33"/>
-      <c r="O12" s="33"/>
-      <c r="P12" s="33"/>
-      <c r="Q12" s="35"/>
-    </row>
-    <row r="13" spans="1:17" s="8" customFormat="1" ht="60" customHeight="1">
+      <c r="H12" s="39"/>
+      <c r="I12" s="39"/>
+      <c r="J12" s="39"/>
+      <c r="K12" s="39"/>
+      <c r="L12" s="39"/>
+      <c r="M12" s="39"/>
+      <c r="N12" s="39"/>
+      <c r="O12" s="39"/>
+      <c r="P12" s="39"/>
+      <c r="Q12" s="40"/>
+    </row>
+    <row r="13" spans="1:17" s="8" customFormat="1" ht="60" hidden="1" customHeight="1">
       <c r="B13" s="19"/>
       <c r="C13" s="19"/>
       <c r="D13" s="19"/>
       <c r="E13" s="19"/>
       <c r="F13" s="19"/>
-      <c r="G13" s="19"/>
-      <c r="H13" s="33"/>
-      <c r="I13" s="33"/>
-      <c r="J13" s="33"/>
-      <c r="K13" s="33"/>
-      <c r="L13" s="33"/>
-      <c r="M13" s="33"/>
-      <c r="N13" s="33"/>
-      <c r="O13" s="33"/>
-      <c r="P13" s="33"/>
-      <c r="Q13" s="35"/>
-    </row>
-    <row r="14" spans="1:17" s="8" customFormat="1" ht="60" customHeight="1">
+      <c r="H13" s="39"/>
+      <c r="I13" s="39"/>
+      <c r="J13" s="39"/>
+      <c r="K13" s="39"/>
+      <c r="L13" s="39"/>
+      <c r="M13" s="39"/>
+      <c r="N13" s="39"/>
+      <c r="O13" s="39"/>
+      <c r="P13" s="39"/>
+      <c r="Q13" s="40"/>
+    </row>
+    <row r="14" spans="1:17" s="8" customFormat="1" ht="60" hidden="1" customHeight="1">
       <c r="B14" s="19"/>
       <c r="C14" s="19"/>
       <c r="D14" s="19"/>
       <c r="E14" s="19"/>
       <c r="F14" s="19"/>
-      <c r="G14" s="19"/>
-      <c r="H14" s="33"/>
-      <c r="I14" s="33"/>
-      <c r="J14" s="33"/>
-      <c r="K14" s="33"/>
-      <c r="L14" s="33"/>
-      <c r="M14" s="33"/>
-      <c r="N14" s="33"/>
-      <c r="O14" s="33"/>
-      <c r="P14" s="33"/>
-      <c r="Q14" s="35"/>
-    </row>
-    <row r="15" spans="1:17" s="8" customFormat="1" ht="60" customHeight="1">
+      <c r="H14" s="39"/>
+      <c r="I14" s="39"/>
+      <c r="J14" s="39"/>
+      <c r="K14" s="39"/>
+      <c r="L14" s="39"/>
+      <c r="M14" s="39"/>
+      <c r="N14" s="39"/>
+      <c r="O14" s="39"/>
+      <c r="P14" s="39"/>
+      <c r="Q14" s="40"/>
+    </row>
+    <row r="15" spans="1:17" s="8" customFormat="1" ht="60" hidden="1" customHeight="1">
       <c r="B15" s="19"/>
       <c r="C15" s="19"/>
       <c r="D15" s="19"/>
       <c r="E15" s="19"/>
       <c r="F15" s="19"/>
-      <c r="G15" s="19"/>
-      <c r="H15" s="33"/>
-      <c r="I15" s="33"/>
-      <c r="J15" s="33"/>
-      <c r="K15" s="33"/>
-      <c r="L15" s="33"/>
-      <c r="M15" s="33"/>
-      <c r="N15" s="33"/>
-      <c r="O15" s="33"/>
-      <c r="P15" s="33"/>
-      <c r="Q15" s="35"/>
-    </row>
-    <row r="16" spans="1:17" s="8" customFormat="1" ht="60" hidden="1" customHeight="1">
-      <c r="B16" s="19"/>
-      <c r="C16" s="19"/>
-      <c r="D16" s="19"/>
-      <c r="E16" s="19"/>
-      <c r="F16" s="19"/>
-      <c r="G16" s="19"/>
-      <c r="H16" s="33"/>
-      <c r="I16" s="33"/>
-      <c r="J16" s="33"/>
-      <c r="K16" s="33"/>
-      <c r="L16" s="33"/>
-      <c r="M16" s="33"/>
-      <c r="N16" s="33"/>
-      <c r="O16" s="33"/>
-      <c r="P16" s="33"/>
-      <c r="Q16" s="35"/>
-    </row>
-    <row r="17" spans="2:17" s="8" customFormat="1" ht="60" hidden="1" customHeight="1">
-      <c r="B17" s="19"/>
-      <c r="C17" s="19"/>
-      <c r="D17" s="19"/>
-      <c r="E17" s="19"/>
-      <c r="F17" s="19"/>
-      <c r="G17" s="19"/>
-      <c r="H17" s="33"/>
-      <c r="I17" s="33"/>
-      <c r="J17" s="33"/>
-      <c r="K17" s="33"/>
-      <c r="L17" s="33"/>
-      <c r="M17" s="33"/>
-      <c r="N17" s="33"/>
-      <c r="O17" s="33"/>
-      <c r="P17" s="33"/>
-      <c r="Q17" s="35"/>
-    </row>
-    <row r="18" spans="2:17" s="8" customFormat="1" ht="60" hidden="1" customHeight="1">
-      <c r="B18" s="19"/>
-      <c r="C18" s="19"/>
-      <c r="D18" s="19"/>
-      <c r="E18" s="19"/>
-      <c r="F18" s="19"/>
-      <c r="G18" s="19"/>
-      <c r="H18" s="33"/>
-      <c r="I18" s="33"/>
-      <c r="J18" s="33"/>
-      <c r="K18" s="33"/>
-      <c r="L18" s="33"/>
-      <c r="M18" s="33"/>
-      <c r="N18" s="33"/>
-      <c r="O18" s="33"/>
-      <c r="P18" s="33"/>
-      <c r="Q18" s="35"/>
+      <c r="H15" s="39"/>
+      <c r="I15" s="39"/>
+      <c r="J15" s="39"/>
+      <c r="K15" s="39"/>
+      <c r="L15" s="39"/>
+      <c r="M15" s="39"/>
+      <c r="N15" s="39"/>
+      <c r="O15" s="39"/>
+      <c r="P15" s="39"/>
+      <c r="Q15" s="40"/>
+    </row>
+    <row r="16" spans="1:17" s="8" customFormat="1" ht="24.75" customHeight="1">
+      <c r="B16" s="26"/>
+      <c r="C16" s="27"/>
+      <c r="D16" s="27"/>
+      <c r="E16" s="27"/>
+      <c r="F16" s="27"/>
+      <c r="H16" s="39"/>
+      <c r="I16" s="39"/>
+      <c r="J16" s="39"/>
+      <c r="K16" s="39"/>
+      <c r="L16" s="39"/>
+      <c r="M16" s="39"/>
+      <c r="N16" s="39"/>
+      <c r="O16" s="39"/>
+      <c r="P16" s="39"/>
+      <c r="Q16" s="40"/>
+    </row>
+    <row r="17" spans="2:17" s="8" customFormat="1" ht="24.75" customHeight="1">
+      <c r="B17" s="28"/>
+      <c r="C17" s="12"/>
+      <c r="D17" s="12"/>
+      <c r="E17" s="12"/>
+      <c r="F17" s="12"/>
+      <c r="G17" s="12"/>
+      <c r="H17" s="12"/>
+      <c r="I17" s="12"/>
+      <c r="J17" s="12"/>
+      <c r="K17" s="12"/>
+      <c r="L17" s="12"/>
+      <c r="M17" s="12"/>
+      <c r="N17" s="12"/>
+      <c r="O17" s="12"/>
+      <c r="P17" s="12"/>
+      <c r="Q17" s="18"/>
+    </row>
+    <row r="18" spans="2:17" s="8" customFormat="1" ht="24.75" customHeight="1">
+      <c r="B18" s="28"/>
+      <c r="C18" s="12"/>
+      <c r="D18" s="12"/>
+      <c r="E18" s="12"/>
+      <c r="F18" s="12"/>
+      <c r="G18" s="12"/>
+      <c r="H18" s="12"/>
+      <c r="I18" s="12"/>
+      <c r="J18" s="12"/>
+      <c r="K18" s="12"/>
+      <c r="L18" s="12"/>
+      <c r="M18" s="12"/>
+      <c r="N18" s="12"/>
+      <c r="O18" s="12"/>
+      <c r="P18" s="12"/>
+      <c r="Q18" s="18"/>
     </row>
     <row r="19" spans="2:17" s="8" customFormat="1" ht="24.75" customHeight="1">
-      <c r="B19" s="30"/>
-      <c r="C19" s="31"/>
-      <c r="D19" s="31"/>
-      <c r="E19" s="31"/>
-      <c r="F19" s="31"/>
-      <c r="G19" s="31"/>
-      <c r="H19" s="33"/>
-      <c r="I19" s="33"/>
-      <c r="J19" s="33"/>
-      <c r="K19" s="33"/>
-      <c r="L19" s="33"/>
-      <c r="M19" s="33"/>
-      <c r="N19" s="33"/>
-      <c r="O19" s="33"/>
-      <c r="P19" s="33"/>
-      <c r="Q19" s="35"/>
+      <c r="B19" s="28"/>
+      <c r="C19" s="12"/>
+      <c r="D19" s="12"/>
+      <c r="E19" s="12"/>
+      <c r="F19" s="12"/>
+      <c r="G19" s="12"/>
+      <c r="H19" s="12"/>
+      <c r="I19" s="12"/>
+      <c r="J19" s="12"/>
+      <c r="K19" s="12"/>
+      <c r="L19" s="12"/>
+      <c r="M19" s="12"/>
+      <c r="N19" s="12"/>
+      <c r="O19" s="12"/>
+      <c r="P19" s="12"/>
+      <c r="Q19" s="18"/>
     </row>
     <row r="20" spans="2:17" s="8" customFormat="1" ht="24.75" customHeight="1">
-      <c r="B20" s="32"/>
-      <c r="C20" s="33"/>
-      <c r="D20" s="33"/>
-      <c r="E20" s="33"/>
-      <c r="F20" s="33"/>
-      <c r="G20" s="33"/>
+      <c r="B20" s="28"/>
+      <c r="C20" s="12"/>
+      <c r="D20" s="12"/>
+      <c r="E20" s="12"/>
+      <c r="G20" s="12"/>
       <c r="H20" s="12"/>
       <c r="I20" s="12"/>
       <c r="J20" s="12"/>
@@ -1469,12 +1475,11 @@
       <c r="Q20" s="18"/>
     </row>
     <row r="21" spans="2:17" s="8" customFormat="1" ht="24.75" customHeight="1">
-      <c r="B21" s="32"/>
-      <c r="C21" s="33"/>
-      <c r="D21" s="33"/>
-      <c r="E21" s="33"/>
-      <c r="F21" s="33"/>
-      <c r="G21" s="33"/>
+      <c r="B21" s="28"/>
+      <c r="C21" s="12"/>
+      <c r="D21" s="12"/>
+      <c r="E21" s="12"/>
+      <c r="G21" s="12"/>
       <c r="H21" s="12"/>
       <c r="I21" s="12"/>
       <c r="J21" s="12"/>
@@ -1487,12 +1492,11 @@
       <c r="Q21" s="18"/>
     </row>
     <row r="22" spans="2:17" s="8" customFormat="1" ht="24.75" customHeight="1">
-      <c r="B22" s="32"/>
-      <c r="C22" s="33"/>
-      <c r="D22" s="33"/>
-      <c r="E22" s="33"/>
-      <c r="F22" s="33"/>
-      <c r="G22" s="33"/>
+      <c r="B22" s="28"/>
+      <c r="C22" s="12"/>
+      <c r="D22" s="12"/>
+      <c r="E22" s="12"/>
+      <c r="G22" s="12"/>
       <c r="H22" s="12"/>
       <c r="I22" s="12"/>
       <c r="J22" s="12"/>
@@ -1504,155 +1508,123 @@
       <c r="P22" s="12"/>
       <c r="Q22" s="18"/>
     </row>
-    <row r="23" spans="2:17" s="8" customFormat="1" ht="24.75" customHeight="1">
-      <c r="B23" s="32"/>
-      <c r="C23" s="33"/>
-      <c r="D23" s="33"/>
-      <c r="E23" s="33"/>
-      <c r="F23" s="33"/>
-      <c r="G23" s="33"/>
-      <c r="H23" s="12"/>
-      <c r="I23" s="12"/>
-      <c r="J23" s="12"/>
-      <c r="K23" s="12"/>
-      <c r="L23" s="12"/>
-      <c r="M23" s="12"/>
-      <c r="N23" s="12"/>
-      <c r="O23" s="12"/>
-      <c r="P23" s="12"/>
-      <c r="Q23" s="18"/>
-    </row>
-    <row r="24" spans="2:17" s="8" customFormat="1" ht="24.75" customHeight="1">
-      <c r="B24" s="32"/>
-      <c r="C24" s="33"/>
-      <c r="D24" s="33"/>
-      <c r="E24" s="33"/>
-      <c r="F24" s="33"/>
-      <c r="G24" s="33"/>
-      <c r="H24" s="12"/>
-      <c r="I24" s="12"/>
-      <c r="J24" s="12"/>
-      <c r="K24" s="12"/>
-      <c r="L24" s="12"/>
-      <c r="M24" s="12"/>
-      <c r="N24" s="12"/>
-      <c r="O24" s="12"/>
-      <c r="P24" s="12"/>
-      <c r="Q24" s="18"/>
-    </row>
-    <row r="25" spans="2:17" s="8" customFormat="1" ht="24.75" customHeight="1">
-      <c r="B25" s="32"/>
-      <c r="C25" s="33"/>
-      <c r="D25" s="33"/>
-      <c r="E25" s="33"/>
-      <c r="F25" s="33"/>
-      <c r="G25" s="33"/>
-      <c r="H25" s="12"/>
-      <c r="I25" s="12"/>
-      <c r="J25" s="12"/>
-      <c r="K25" s="12"/>
-      <c r="L25" s="12"/>
-      <c r="M25" s="12"/>
-      <c r="N25" s="12"/>
-      <c r="O25" s="12"/>
-      <c r="P25" s="12"/>
-      <c r="Q25" s="18"/>
-    </row>
-    <row r="26" spans="2:17" s="11" customFormat="1" ht="30.75" customHeight="1" thickBot="1">
-      <c r="B26" s="20"/>
-      <c r="C26" s="20"/>
-      <c r="D26" s="20"/>
-      <c r="E26" s="20"/>
-      <c r="F26" s="20"/>
-      <c r="G26" s="20"/>
-      <c r="H26" s="20"/>
-      <c r="I26" s="20"/>
-      <c r="J26" s="20"/>
-      <c r="K26" s="20"/>
-      <c r="L26" s="20"/>
-      <c r="M26" s="20"/>
-      <c r="N26" s="20"/>
-      <c r="O26" s="20"/>
-      <c r="P26" s="20"/>
+    <row r="23" spans="2:17" s="11" customFormat="1" ht="30.75" customHeight="1" thickBot="1">
+      <c r="B23" s="20"/>
+      <c r="C23" s="20"/>
+      <c r="D23" s="20"/>
+      <c r="E23" s="20"/>
+      <c r="F23" s="12"/>
+      <c r="G23" s="20"/>
+      <c r="H23" s="20"/>
+      <c r="I23" s="20"/>
+      <c r="J23" s="20"/>
+      <c r="K23" s="20"/>
+      <c r="L23" s="20"/>
+      <c r="M23" s="20"/>
+      <c r="N23" s="20"/>
+      <c r="O23" s="20"/>
+      <c r="P23" s="20"/>
+      <c r="Q23" s="12"/>
+    </row>
+    <row r="24" spans="2:17" s="8" customFormat="1" ht="30.75" customHeight="1">
+      <c r="B24" s="48" t="s">
+        <v>45</v>
+      </c>
+      <c r="C24" s="48"/>
+      <c r="D24" s="21"/>
+      <c r="E24" s="22"/>
+      <c r="F24" s="2"/>
+      <c r="G24" s="25" t="s">
+        <v>47</v>
+      </c>
+      <c r="H24" s="21"/>
+      <c r="I24" s="22"/>
+      <c r="J24" s="48" t="s">
+        <v>48</v>
+      </c>
+      <c r="K24" s="48"/>
+      <c r="L24" s="21"/>
+      <c r="M24" s="22"/>
+      <c r="N24" s="22"/>
+      <c r="O24" s="48" t="s">
+        <v>49</v>
+      </c>
+      <c r="P24" s="48"/>
+      <c r="Q24" s="1"/>
+    </row>
+    <row r="25" spans="2:17" s="11" customFormat="1" ht="20.25">
+      <c r="B25" s="30" t="s">
+        <v>46</v>
+      </c>
+      <c r="C25" s="30"/>
+      <c r="D25" s="23"/>
+      <c r="E25" s="24"/>
+      <c r="F25" s="2"/>
+      <c r="G25" s="29" t="s">
+        <v>50</v>
+      </c>
+      <c r="H25" s="23"/>
+      <c r="I25" s="24"/>
+      <c r="J25" s="31" t="s">
+        <v>51</v>
+      </c>
+      <c r="K25" s="31"/>
+      <c r="L25" s="23"/>
+      <c r="M25" s="24"/>
+      <c r="N25" s="24"/>
+      <c r="O25" s="32" t="s">
+        <v>52</v>
+      </c>
+      <c r="P25" s="32"/>
+      <c r="Q25" s="12"/>
+    </row>
+    <row r="26" spans="2:17" s="11" customFormat="1">
+      <c r="B26" s="12"/>
+      <c r="C26" s="12"/>
+      <c r="D26" s="12"/>
+      <c r="E26" s="12"/>
+      <c r="F26" s="2"/>
+      <c r="G26" s="12"/>
+      <c r="H26" s="12"/>
+      <c r="I26" s="12"/>
+      <c r="J26" s="12"/>
+      <c r="K26" s="12"/>
+      <c r="L26" s="12"/>
+      <c r="M26" s="12"/>
+      <c r="N26" s="12"/>
+      <c r="O26" s="12"/>
+      <c r="P26" s="12"/>
       <c r="Q26" s="12"/>
     </row>
-    <row r="27" spans="2:17" s="8" customFormat="1" ht="30.75" customHeight="1">
-      <c r="B27" s="27" t="s">
-        <v>48</v>
-      </c>
-      <c r="C27" s="27"/>
-      <c r="D27" s="21"/>
-      <c r="E27" s="22"/>
-      <c r="F27" s="27" t="s">
-        <v>50</v>
-      </c>
-      <c r="G27" s="27"/>
-      <c r="H27" s="21"/>
-      <c r="I27" s="22"/>
-      <c r="J27" s="27" t="s">
-        <v>51</v>
-      </c>
-      <c r="K27" s="27"/>
-      <c r="L27" s="21"/>
-      <c r="M27" s="22"/>
-      <c r="N27" s="22"/>
-      <c r="O27" s="27" t="s">
-        <v>52</v>
-      </c>
-      <c r="P27" s="27"/>
-      <c r="Q27" s="1"/>
-    </row>
-    <row r="28" spans="2:17" s="11" customFormat="1" ht="20.25">
-      <c r="B28" s="41" t="s">
-        <v>49</v>
-      </c>
-      <c r="C28" s="41"/>
-      <c r="D28" s="23"/>
-      <c r="E28" s="24"/>
-      <c r="F28" s="42" t="s">
-        <v>53</v>
-      </c>
-      <c r="G28" s="42"/>
-      <c r="H28" s="23"/>
-      <c r="I28" s="24"/>
-      <c r="J28" s="43" t="s">
-        <v>54</v>
-      </c>
-      <c r="K28" s="43"/>
-      <c r="L28" s="23"/>
-      <c r="M28" s="24"/>
-      <c r="N28" s="24"/>
-      <c r="O28" s="44" t="s">
-        <v>55</v>
-      </c>
-      <c r="P28" s="44"/>
-      <c r="Q28" s="12"/>
-    </row>
-    <row r="29" spans="2:17" s="11" customFormat="1">
-      <c r="B29" s="12"/>
-      <c r="C29" s="12"/>
-      <c r="D29" s="12"/>
-      <c r="E29" s="12"/>
-      <c r="F29" s="12"/>
-      <c r="G29" s="12"/>
-      <c r="H29" s="12"/>
-      <c r="I29" s="12"/>
-      <c r="J29" s="12"/>
-      <c r="K29" s="12"/>
-      <c r="L29" s="12"/>
-      <c r="M29" s="12"/>
-      <c r="N29" s="12"/>
-      <c r="O29" s="12"/>
-      <c r="P29" s="12"/>
-      <c r="Q29" s="12"/>
-    </row>
-    <row r="32" spans="2:17" ht="31.5" customHeight="1"/>
+    <row r="29" spans="2:17" ht="31.5" customHeight="1"/>
   </sheetData>
-  <mergeCells count="41">
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="O28:P28"/>
+  <mergeCells count="39">
+    <mergeCell ref="G1:M1"/>
+    <mergeCell ref="H2:M2"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="O24:P24"/>
+    <mergeCell ref="B3:Q3"/>
+    <mergeCell ref="O1:Q1"/>
+    <mergeCell ref="B4:Q4"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="G7:G8"/>
+    <mergeCell ref="E7:E8"/>
+    <mergeCell ref="L7:L8"/>
+    <mergeCell ref="J7:J8"/>
+    <mergeCell ref="F7:F8"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="C7:C8"/>
+    <mergeCell ref="D7:D8"/>
+    <mergeCell ref="H7:H8"/>
+    <mergeCell ref="Q5:Q6"/>
+    <mergeCell ref="N5:N6"/>
+    <mergeCell ref="O5:O6"/>
+    <mergeCell ref="M7:M8"/>
+    <mergeCell ref="K7:K8"/>
+    <mergeCell ref="I7:I8"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="O25:P25"/>
     <mergeCell ref="I5:J5"/>
     <mergeCell ref="C5:C6"/>
     <mergeCell ref="D5:D6"/>
@@ -1665,31 +1637,7 @@
     <mergeCell ref="M5:M6"/>
     <mergeCell ref="B5:B6"/>
     <mergeCell ref="P5:P6"/>
-    <mergeCell ref="H7:H8"/>
-    <mergeCell ref="Q5:Q6"/>
-    <mergeCell ref="N5:N6"/>
-    <mergeCell ref="O5:O6"/>
-    <mergeCell ref="M7:M8"/>
-    <mergeCell ref="K7:K8"/>
-    <mergeCell ref="I7:I8"/>
-    <mergeCell ref="B4:Q4"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="G7:G8"/>
-    <mergeCell ref="E7:E8"/>
-    <mergeCell ref="L7:L8"/>
-    <mergeCell ref="J7:J8"/>
-    <mergeCell ref="F7:F8"/>
-    <mergeCell ref="B7:B8"/>
-    <mergeCell ref="C7:C8"/>
-    <mergeCell ref="D7:D8"/>
-    <mergeCell ref="B19:G25"/>
-    <mergeCell ref="H9:Q19"/>
-    <mergeCell ref="G1:M1"/>
-    <mergeCell ref="H2:M2"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="O27:P27"/>
-    <mergeCell ref="B3:Q3"/>
+    <mergeCell ref="H9:Q16"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.25" top="0.25" bottom="0.5" header="0" footer="0"/>
   <pageSetup paperSize="9" scale="52" fitToHeight="0" orientation="landscape" r:id="rId1"/>

--- a/APLOS/POPResources/Templates/MlrBengali20181.xlsx
+++ b/APLOS/POPResources/Templates/MlrBengali20181.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26327"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26924"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\AplosProject\APLOS\POPResources\Templates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Projects\Aplos.New\APLOS\POPResources\Templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41D870E4-8DF3-4822-A41C-3A9631AB26FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10845735-2D2A-465D-AF41-9B9FF83E4621}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -195,13 +195,13 @@
     <t>বেসিক এ্যাপারেলস লিঃ</t>
   </si>
   <si>
-    <t>১৩৫-১৩৮, (২য়-৫ম তলা ) আবদুল্লাহপুর, উত্তরা, ঢাকা-১২৩০</t>
-  </si>
-  <si>
     <t>(বাংলাদেশ শ্রম আইন ২০০৬ এবং সংশোধিত ২০২২ এর ধারা আনুযায়ী)</t>
   </si>
   <si>
     <t>(বাংলাদেশ শ্রম আইন ২০০৬ এবং নতুন সংশোধিত ২০২২ এর ধারা ৪৮ (২) অনুযায়ী প্রসূতিকল্যান সুবিধা হিসাব করিবার ক্ষেত্রে শ্রমিকের সর্বশেষ মাসিক প্রাপ্ত মোট মজুরীকে ২৬ দ্বারা ভাগ করিয়া ০১ দিনের গড় মজুরী নির্ধারন করিতে হইবে। দৈনিক গড় মজুরী (টাকা)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">১৩৫-১৩৮, (২য়-৫ম তলা ) আবদুল্লাহপুর, উত্তরা, ঢাকা-১২৩০ </t>
   </si>
 </sst>
 </file>
@@ -565,6 +565,51 @@
     <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -580,12 +625,6 @@
     <xf numFmtId="164" fontId="6" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -597,45 +636,6 @@
     </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -998,24 +998,24 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:Q29"/>
-  <sheetFormatPr defaultRowHeight="18"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="17.399999999999999"/>
   <cols>
     <col min="1" max="1" width="37" style="4" hidden="1" customWidth="1"/>
-    <col min="2" max="2" width="24.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.109375" style="2" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="19" style="2" customWidth="1"/>
-    <col min="4" max="4" width="19.5703125" style="2" customWidth="1"/>
-    <col min="5" max="5" width="23.28515625" style="2" customWidth="1"/>
-    <col min="6" max="7" width="22.42578125" style="2" customWidth="1"/>
-    <col min="8" max="8" width="26.28515625" style="2" customWidth="1"/>
-    <col min="9" max="10" width="17.85546875" style="2" customWidth="1"/>
+    <col min="4" max="4" width="19.5546875" style="2" customWidth="1"/>
+    <col min="5" max="5" width="23.33203125" style="2" customWidth="1"/>
+    <col min="6" max="7" width="22.44140625" style="2" customWidth="1"/>
+    <col min="8" max="8" width="26.33203125" style="2" customWidth="1"/>
+    <col min="9" max="10" width="17.88671875" style="2" customWidth="1"/>
     <col min="11" max="11" width="19" style="2" customWidth="1"/>
-    <col min="12" max="12" width="18.42578125" style="2" customWidth="1"/>
-    <col min="13" max="13" width="19.5703125" style="2" customWidth="1"/>
-    <col min="14" max="14" width="20.28515625" style="3" customWidth="1"/>
-    <col min="15" max="15" width="20.7109375" style="3" customWidth="1"/>
-    <col min="16" max="16" width="19.42578125" style="3" customWidth="1"/>
-    <col min="17" max="17" width="34.140625" style="3" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="4"/>
+    <col min="12" max="12" width="18.44140625" style="2" customWidth="1"/>
+    <col min="13" max="13" width="19.5546875" style="2" customWidth="1"/>
+    <col min="14" max="14" width="20.33203125" style="3" customWidth="1"/>
+    <col min="15" max="15" width="20.6640625" style="3" customWidth="1"/>
+    <col min="16" max="16" width="19.44140625" style="3" customWidth="1"/>
+    <col min="17" max="17" width="34.109375" style="3" customWidth="1"/>
+    <col min="18" max="16384" width="9.109375" style="4"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="68.25" customHeight="1">
@@ -1024,19 +1024,19 @@
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
-      <c r="G1" s="46" t="s">
+      <c r="G1" s="30" t="s">
         <v>55</v>
       </c>
-      <c r="H1" s="46"/>
-      <c r="I1" s="46"/>
-      <c r="J1" s="46"/>
-      <c r="K1" s="46"/>
-      <c r="L1" s="46"/>
-      <c r="M1" s="46"/>
+      <c r="H1" s="30"/>
+      <c r="I1" s="30"/>
+      <c r="J1" s="30"/>
+      <c r="K1" s="30"/>
+      <c r="L1" s="30"/>
+      <c r="M1" s="30"/>
       <c r="N1" s="1"/>
-      <c r="O1" s="51"/>
-      <c r="P1" s="52"/>
-      <c r="Q1" s="52"/>
+      <c r="O1" s="35"/>
+      <c r="P1" s="36"/>
+      <c r="Q1" s="36"/>
     </row>
     <row r="2" spans="1:17" ht="46.5" customHeight="1">
       <c r="B2" s="5"/>
@@ -1044,166 +1044,166 @@
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
-      <c r="H2" s="47" t="s">
-        <v>56</v>
-      </c>
-      <c r="I2" s="47"/>
-      <c r="J2" s="47"/>
-      <c r="K2" s="47"/>
-      <c r="L2" s="47"/>
-      <c r="M2" s="47"/>
+      <c r="H2" s="31" t="s">
+        <v>58</v>
+      </c>
+      <c r="I2" s="31"/>
+      <c r="J2" s="31"/>
+      <c r="K2" s="31"/>
+      <c r="L2" s="31"/>
+      <c r="M2" s="31"/>
       <c r="N2" s="1"/>
       <c r="O2" s="1"/>
     </row>
     <row r="3" spans="1:17" s="6" customFormat="1" ht="50.25" customHeight="1">
-      <c r="B3" s="49" t="s">
+      <c r="B3" s="33" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="50"/>
-      <c r="D3" s="50"/>
-      <c r="E3" s="50"/>
-      <c r="F3" s="50"/>
-      <c r="G3" s="50"/>
-      <c r="H3" s="50"/>
-      <c r="I3" s="50"/>
-      <c r="J3" s="50"/>
-      <c r="K3" s="50"/>
-      <c r="L3" s="50"/>
-      <c r="M3" s="50"/>
-      <c r="N3" s="50"/>
-      <c r="O3" s="50"/>
-      <c r="P3" s="50"/>
-      <c r="Q3" s="50"/>
+      <c r="C3" s="34"/>
+      <c r="D3" s="34"/>
+      <c r="E3" s="34"/>
+      <c r="F3" s="34"/>
+      <c r="G3" s="34"/>
+      <c r="H3" s="34"/>
+      <c r="I3" s="34"/>
+      <c r="J3" s="34"/>
+      <c r="K3" s="34"/>
+      <c r="L3" s="34"/>
+      <c r="M3" s="34"/>
+      <c r="N3" s="34"/>
+      <c r="O3" s="34"/>
+      <c r="P3" s="34"/>
+      <c r="Q3" s="34"/>
     </row>
     <row r="4" spans="1:17" s="6" customFormat="1" ht="48.75" customHeight="1">
       <c r="A4"/>
-      <c r="B4" s="53" t="s">
+      <c r="B4" s="37" t="s">
+        <v>56</v>
+      </c>
+      <c r="C4" s="37"/>
+      <c r="D4" s="37"/>
+      <c r="E4" s="37"/>
+      <c r="F4" s="37"/>
+      <c r="G4" s="37"/>
+      <c r="H4" s="37"/>
+      <c r="I4" s="37"/>
+      <c r="J4" s="37"/>
+      <c r="K4" s="37"/>
+      <c r="L4" s="37"/>
+      <c r="M4" s="37"/>
+      <c r="N4" s="37"/>
+      <c r="O4" s="37"/>
+      <c r="P4" s="37"/>
+      <c r="Q4" s="37"/>
+    </row>
+    <row r="5" spans="1:17" s="7" customFormat="1" ht="251.25" customHeight="1">
+      <c r="B5" s="43" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" s="43" t="s">
+        <v>1</v>
+      </c>
+      <c r="D5" s="43" t="s">
+        <v>0</v>
+      </c>
+      <c r="E5" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="F5" s="43" t="s">
+        <v>5</v>
+      </c>
+      <c r="G5" s="43" t="s">
+        <v>6</v>
+      </c>
+      <c r="H5" s="43" t="s">
+        <v>7</v>
+      </c>
+      <c r="I5" s="48" t="s">
         <v>57</v>
       </c>
-      <c r="C4" s="53"/>
-      <c r="D4" s="53"/>
-      <c r="E4" s="53"/>
-      <c r="F4" s="53"/>
-      <c r="G4" s="53"/>
-      <c r="H4" s="53"/>
-      <c r="I4" s="53"/>
-      <c r="J4" s="53"/>
-      <c r="K4" s="53"/>
-      <c r="L4" s="53"/>
-      <c r="M4" s="53"/>
-      <c r="N4" s="53"/>
-      <c r="O4" s="53"/>
-      <c r="P4" s="53"/>
-      <c r="Q4" s="53"/>
-    </row>
-    <row r="5" spans="1:17" s="7" customFormat="1" ht="251.25" customHeight="1">
-      <c r="B5" s="35" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" s="35" t="s">
-        <v>1</v>
-      </c>
-      <c r="D5" s="35" t="s">
-        <v>0</v>
-      </c>
-      <c r="E5" s="35" t="s">
-        <v>4</v>
-      </c>
-      <c r="F5" s="35" t="s">
-        <v>5</v>
-      </c>
-      <c r="G5" s="35" t="s">
-        <v>6</v>
-      </c>
-      <c r="H5" s="35" t="s">
-        <v>7</v>
-      </c>
-      <c r="I5" s="33" t="s">
-        <v>58</v>
-      </c>
-      <c r="J5" s="34"/>
-      <c r="K5" s="35" t="s">
+      <c r="J5" s="49"/>
+      <c r="K5" s="43" t="s">
         <v>8</v>
       </c>
-      <c r="L5" s="35" t="s">
+      <c r="L5" s="43" t="s">
         <v>53</v>
       </c>
-      <c r="M5" s="35" t="s">
+      <c r="M5" s="43" t="s">
         <v>11</v>
       </c>
-      <c r="N5" s="44" t="s">
+      <c r="N5" s="41" t="s">
         <v>9</v>
       </c>
-      <c r="O5" s="35" t="s">
+      <c r="O5" s="43" t="s">
         <v>10</v>
       </c>
-      <c r="P5" s="35" t="s">
+      <c r="P5" s="43" t="s">
         <v>54</v>
       </c>
-      <c r="Q5" s="43" t="s">
+      <c r="Q5" s="40" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:17" s="8" customFormat="1" ht="93">
-      <c r="B6" s="36"/>
-      <c r="C6" s="36"/>
-      <c r="D6" s="36"/>
-      <c r="E6" s="36"/>
-      <c r="F6" s="36"/>
-      <c r="G6" s="36"/>
-      <c r="H6" s="36"/>
+    <row r="6" spans="1:17" s="8" customFormat="1" ht="91.2">
+      <c r="B6" s="44"/>
+      <c r="C6" s="44"/>
+      <c r="D6" s="44"/>
+      <c r="E6" s="44"/>
+      <c r="F6" s="44"/>
+      <c r="G6" s="44"/>
+      <c r="H6" s="44"/>
       <c r="I6" s="15" t="s">
         <v>12</v>
       </c>
       <c r="J6" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="K6" s="36"/>
-      <c r="L6" s="36"/>
-      <c r="M6" s="36"/>
-      <c r="N6" s="45"/>
-      <c r="O6" s="36"/>
-      <c r="P6" s="36"/>
-      <c r="Q6" s="42"/>
+      <c r="K6" s="44"/>
+      <c r="L6" s="44"/>
+      <c r="M6" s="44"/>
+      <c r="N6" s="42"/>
+      <c r="O6" s="44"/>
+      <c r="P6" s="44"/>
+      <c r="Q6" s="39"/>
     </row>
     <row r="7" spans="1:17" s="8" customFormat="1" ht="120" customHeight="1">
       <c r="A7" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="B7" s="41" t="s">
+      <c r="B7" s="38" t="s">
         <v>36</v>
       </c>
-      <c r="C7" s="41" t="s">
+      <c r="C7" s="38" t="s">
         <v>37</v>
       </c>
-      <c r="D7" s="41" t="s">
+      <c r="D7" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="E7" s="41" t="s">
+      <c r="E7" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="F7" s="41" t="s">
+      <c r="F7" s="38" t="s">
         <v>38</v>
       </c>
-      <c r="G7" s="41" t="s">
+      <c r="G7" s="38" t="s">
         <v>23</v>
       </c>
-      <c r="H7" s="41" t="s">
+      <c r="H7" s="38" t="s">
         <v>43</v>
       </c>
-      <c r="I7" s="41" t="s">
+      <c r="I7" s="38" t="s">
         <v>42</v>
       </c>
-      <c r="J7" s="41" t="s">
+      <c r="J7" s="38" t="s">
         <v>25</v>
       </c>
-      <c r="K7" s="41" t="s">
+      <c r="K7" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="L7" s="41" t="s">
+      <c r="L7" s="38" t="s">
         <v>24</v>
       </c>
-      <c r="M7" s="41" t="s">
+      <c r="M7" s="38" t="s">
         <v>27</v>
       </c>
       <c r="N7" s="16" t="s">
@@ -1219,18 +1219,18 @@
       <c r="A8" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="B8" s="42"/>
-      <c r="C8" s="42"/>
-      <c r="D8" s="42"/>
-      <c r="E8" s="42"/>
-      <c r="F8" s="42"/>
-      <c r="G8" s="42"/>
-      <c r="H8" s="42"/>
-      <c r="I8" s="42"/>
-      <c r="J8" s="42"/>
-      <c r="K8" s="42"/>
-      <c r="L8" s="42"/>
-      <c r="M8" s="42"/>
+      <c r="B8" s="39"/>
+      <c r="C8" s="39"/>
+      <c r="D8" s="39"/>
+      <c r="E8" s="39"/>
+      <c r="F8" s="39"/>
+      <c r="G8" s="39"/>
+      <c r="H8" s="39"/>
+      <c r="I8" s="39"/>
+      <c r="J8" s="39"/>
+      <c r="K8" s="39"/>
+      <c r="L8" s="39"/>
+      <c r="M8" s="39"/>
       <c r="N8" s="16" t="s">
         <v>21</v>
       </c>
@@ -1247,16 +1247,16 @@
       <c r="E9" s="1"/>
       <c r="F9" s="1"/>
       <c r="G9" s="1"/>
-      <c r="H9" s="37"/>
-      <c r="I9" s="37"/>
-      <c r="J9" s="37"/>
-      <c r="K9" s="37"/>
-      <c r="L9" s="37"/>
-      <c r="M9" s="37"/>
-      <c r="N9" s="37"/>
-      <c r="O9" s="37"/>
-      <c r="P9" s="37"/>
-      <c r="Q9" s="38"/>
+      <c r="H9" s="50"/>
+      <c r="I9" s="50"/>
+      <c r="J9" s="50"/>
+      <c r="K9" s="50"/>
+      <c r="L9" s="50"/>
+      <c r="M9" s="50"/>
+      <c r="N9" s="50"/>
+      <c r="O9" s="50"/>
+      <c r="P9" s="50"/>
+      <c r="Q9" s="51"/>
     </row>
     <row r="10" spans="1:17" s="11" customFormat="1" ht="55.5" customHeight="1">
       <c r="A10" s="10" t="s">
@@ -1277,16 +1277,16 @@
       <c r="F10" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="H10" s="39"/>
-      <c r="I10" s="39"/>
-      <c r="J10" s="39"/>
-      <c r="K10" s="39"/>
-      <c r="L10" s="39"/>
-      <c r="M10" s="39"/>
-      <c r="N10" s="39"/>
-      <c r="O10" s="39"/>
-      <c r="P10" s="39"/>
-      <c r="Q10" s="40"/>
+      <c r="H10" s="52"/>
+      <c r="I10" s="52"/>
+      <c r="J10" s="52"/>
+      <c r="K10" s="52"/>
+      <c r="L10" s="52"/>
+      <c r="M10" s="52"/>
+      <c r="N10" s="52"/>
+      <c r="O10" s="52"/>
+      <c r="P10" s="52"/>
+      <c r="Q10" s="53"/>
     </row>
     <row r="11" spans="1:17" s="8" customFormat="1" ht="56.25" customHeight="1">
       <c r="A11" s="8" t="s">
@@ -1307,16 +1307,16 @@
       <c r="F11" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="H11" s="39"/>
-      <c r="I11" s="39"/>
-      <c r="J11" s="39"/>
-      <c r="K11" s="39"/>
-      <c r="L11" s="39"/>
-      <c r="M11" s="39"/>
-      <c r="N11" s="39"/>
-      <c r="O11" s="39"/>
-      <c r="P11" s="39"/>
-      <c r="Q11" s="40"/>
+      <c r="H11" s="52"/>
+      <c r="I11" s="52"/>
+      <c r="J11" s="52"/>
+      <c r="K11" s="52"/>
+      <c r="L11" s="52"/>
+      <c r="M11" s="52"/>
+      <c r="N11" s="52"/>
+      <c r="O11" s="52"/>
+      <c r="P11" s="52"/>
+      <c r="Q11" s="53"/>
     </row>
     <row r="12" spans="1:17" s="8" customFormat="1" ht="60" customHeight="1">
       <c r="B12" s="19"/>
@@ -1324,16 +1324,16 @@
       <c r="D12" s="19"/>
       <c r="E12" s="19"/>
       <c r="F12" s="19"/>
-      <c r="H12" s="39"/>
-      <c r="I12" s="39"/>
-      <c r="J12" s="39"/>
-      <c r="K12" s="39"/>
-      <c r="L12" s="39"/>
-      <c r="M12" s="39"/>
-      <c r="N12" s="39"/>
-      <c r="O12" s="39"/>
-      <c r="P12" s="39"/>
-      <c r="Q12" s="40"/>
+      <c r="H12" s="52"/>
+      <c r="I12" s="52"/>
+      <c r="J12" s="52"/>
+      <c r="K12" s="52"/>
+      <c r="L12" s="52"/>
+      <c r="M12" s="52"/>
+      <c r="N12" s="52"/>
+      <c r="O12" s="52"/>
+      <c r="P12" s="52"/>
+      <c r="Q12" s="53"/>
     </row>
     <row r="13" spans="1:17" s="8" customFormat="1" ht="60" hidden="1" customHeight="1">
       <c r="B13" s="19"/>
@@ -1341,16 +1341,16 @@
       <c r="D13" s="19"/>
       <c r="E13" s="19"/>
       <c r="F13" s="19"/>
-      <c r="H13" s="39"/>
-      <c r="I13" s="39"/>
-      <c r="J13" s="39"/>
-      <c r="K13" s="39"/>
-      <c r="L13" s="39"/>
-      <c r="M13" s="39"/>
-      <c r="N13" s="39"/>
-      <c r="O13" s="39"/>
-      <c r="P13" s="39"/>
-      <c r="Q13" s="40"/>
+      <c r="H13" s="52"/>
+      <c r="I13" s="52"/>
+      <c r="J13" s="52"/>
+      <c r="K13" s="52"/>
+      <c r="L13" s="52"/>
+      <c r="M13" s="52"/>
+      <c r="N13" s="52"/>
+      <c r="O13" s="52"/>
+      <c r="P13" s="52"/>
+      <c r="Q13" s="53"/>
     </row>
     <row r="14" spans="1:17" s="8" customFormat="1" ht="60" hidden="1" customHeight="1">
       <c r="B14" s="19"/>
@@ -1358,16 +1358,16 @@
       <c r="D14" s="19"/>
       <c r="E14" s="19"/>
       <c r="F14" s="19"/>
-      <c r="H14" s="39"/>
-      <c r="I14" s="39"/>
-      <c r="J14" s="39"/>
-      <c r="K14" s="39"/>
-      <c r="L14" s="39"/>
-      <c r="M14" s="39"/>
-      <c r="N14" s="39"/>
-      <c r="O14" s="39"/>
-      <c r="P14" s="39"/>
-      <c r="Q14" s="40"/>
+      <c r="H14" s="52"/>
+      <c r="I14" s="52"/>
+      <c r="J14" s="52"/>
+      <c r="K14" s="52"/>
+      <c r="L14" s="52"/>
+      <c r="M14" s="52"/>
+      <c r="N14" s="52"/>
+      <c r="O14" s="52"/>
+      <c r="P14" s="52"/>
+      <c r="Q14" s="53"/>
     </row>
     <row r="15" spans="1:17" s="8" customFormat="1" ht="60" hidden="1" customHeight="1">
       <c r="B15" s="19"/>
@@ -1375,16 +1375,16 @@
       <c r="D15" s="19"/>
       <c r="E15" s="19"/>
       <c r="F15" s="19"/>
-      <c r="H15" s="39"/>
-      <c r="I15" s="39"/>
-      <c r="J15" s="39"/>
-      <c r="K15" s="39"/>
-      <c r="L15" s="39"/>
-      <c r="M15" s="39"/>
-      <c r="N15" s="39"/>
-      <c r="O15" s="39"/>
-      <c r="P15" s="39"/>
-      <c r="Q15" s="40"/>
+      <c r="H15" s="52"/>
+      <c r="I15" s="52"/>
+      <c r="J15" s="52"/>
+      <c r="K15" s="52"/>
+      <c r="L15" s="52"/>
+      <c r="M15" s="52"/>
+      <c r="N15" s="52"/>
+      <c r="O15" s="52"/>
+      <c r="P15" s="52"/>
+      <c r="Q15" s="53"/>
     </row>
     <row r="16" spans="1:17" s="8" customFormat="1" ht="24.75" customHeight="1">
       <c r="B16" s="26"/>
@@ -1392,16 +1392,16 @@
       <c r="D16" s="27"/>
       <c r="E16" s="27"/>
       <c r="F16" s="27"/>
-      <c r="H16" s="39"/>
-      <c r="I16" s="39"/>
-      <c r="J16" s="39"/>
-      <c r="K16" s="39"/>
-      <c r="L16" s="39"/>
-      <c r="M16" s="39"/>
-      <c r="N16" s="39"/>
-      <c r="O16" s="39"/>
-      <c r="P16" s="39"/>
-      <c r="Q16" s="40"/>
+      <c r="H16" s="52"/>
+      <c r="I16" s="52"/>
+      <c r="J16" s="52"/>
+      <c r="K16" s="52"/>
+      <c r="L16" s="52"/>
+      <c r="M16" s="52"/>
+      <c r="N16" s="52"/>
+      <c r="O16" s="52"/>
+      <c r="P16" s="52"/>
+      <c r="Q16" s="53"/>
     </row>
     <row r="17" spans="2:17" s="8" customFormat="1" ht="24.75" customHeight="1">
       <c r="B17" s="28"/>
@@ -1527,10 +1527,10 @@
       <c r="Q23" s="12"/>
     </row>
     <row r="24" spans="2:17" s="8" customFormat="1" ht="30.75" customHeight="1">
-      <c r="B24" s="48" t="s">
+      <c r="B24" s="32" t="s">
         <v>45</v>
       </c>
-      <c r="C24" s="48"/>
+      <c r="C24" s="32"/>
       <c r="D24" s="21"/>
       <c r="E24" s="22"/>
       <c r="F24" s="2"/>
@@ -1539,24 +1539,24 @@
       </c>
       <c r="H24" s="21"/>
       <c r="I24" s="22"/>
-      <c r="J24" s="48" t="s">
+      <c r="J24" s="32" t="s">
         <v>48</v>
       </c>
-      <c r="K24" s="48"/>
+      <c r="K24" s="32"/>
       <c r="L24" s="21"/>
       <c r="M24" s="22"/>
       <c r="N24" s="22"/>
-      <c r="O24" s="48" t="s">
+      <c r="O24" s="32" t="s">
         <v>49</v>
       </c>
-      <c r="P24" s="48"/>
+      <c r="P24" s="32"/>
       <c r="Q24" s="1"/>
     </row>
-    <row r="25" spans="2:17" s="11" customFormat="1" ht="20.25">
-      <c r="B25" s="30" t="s">
+    <row r="25" spans="2:17" s="11" customFormat="1" ht="20.399999999999999">
+      <c r="B25" s="45" t="s">
         <v>46</v>
       </c>
-      <c r="C25" s="30"/>
+      <c r="C25" s="45"/>
       <c r="D25" s="23"/>
       <c r="E25" s="24"/>
       <c r="F25" s="2"/>
@@ -1565,17 +1565,17 @@
       </c>
       <c r="H25" s="23"/>
       <c r="I25" s="24"/>
-      <c r="J25" s="31" t="s">
+      <c r="J25" s="46" t="s">
         <v>51</v>
       </c>
-      <c r="K25" s="31"/>
+      <c r="K25" s="46"/>
       <c r="L25" s="23"/>
       <c r="M25" s="24"/>
       <c r="N25" s="24"/>
-      <c r="O25" s="32" t="s">
+      <c r="O25" s="47" t="s">
         <v>52</v>
       </c>
-      <c r="P25" s="32"/>
+      <c r="P25" s="47"/>
       <c r="Q25" s="12"/>
     </row>
     <row r="26" spans="2:17" s="11" customFormat="1">
@@ -1599,6 +1599,29 @@
     <row r="29" spans="2:17" ht="31.5" customHeight="1"/>
   </sheetData>
   <mergeCells count="39">
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="O25:P25"/>
+    <mergeCell ref="I5:J5"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="E5:E6"/>
+    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="G5:G6"/>
+    <mergeCell ref="H5:H6"/>
+    <mergeCell ref="K5:K6"/>
+    <mergeCell ref="L5:L6"/>
+    <mergeCell ref="M5:M6"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="P5:P6"/>
+    <mergeCell ref="H9:Q16"/>
+    <mergeCell ref="H7:H8"/>
+    <mergeCell ref="Q5:Q6"/>
+    <mergeCell ref="N5:N6"/>
+    <mergeCell ref="O5:O6"/>
+    <mergeCell ref="M7:M8"/>
+    <mergeCell ref="K7:K8"/>
+    <mergeCell ref="I7:I8"/>
     <mergeCell ref="G1:M1"/>
     <mergeCell ref="H2:M2"/>
     <mergeCell ref="J24:K24"/>
@@ -1615,29 +1638,6 @@
     <mergeCell ref="B7:B8"/>
     <mergeCell ref="C7:C8"/>
     <mergeCell ref="D7:D8"/>
-    <mergeCell ref="H7:H8"/>
-    <mergeCell ref="Q5:Q6"/>
-    <mergeCell ref="N5:N6"/>
-    <mergeCell ref="O5:O6"/>
-    <mergeCell ref="M7:M8"/>
-    <mergeCell ref="K7:K8"/>
-    <mergeCell ref="I7:I8"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="O25:P25"/>
-    <mergeCell ref="I5:J5"/>
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="D5:D6"/>
-    <mergeCell ref="E5:E6"/>
-    <mergeCell ref="F5:F6"/>
-    <mergeCell ref="G5:G6"/>
-    <mergeCell ref="H5:H6"/>
-    <mergeCell ref="K5:K6"/>
-    <mergeCell ref="L5:L6"/>
-    <mergeCell ref="M5:M6"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="P5:P6"/>
-    <mergeCell ref="H9:Q16"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.25" top="0.25" bottom="0.5" header="0" footer="0"/>
   <pageSetup paperSize="9" scale="52" fitToHeight="0" orientation="landscape" r:id="rId1"/>

--- a/APLOS/POPResources/Templates/MlrBengali20181.xlsx
+++ b/APLOS/POPResources/Templates/MlrBengali20181.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26924"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26327"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Projects\Aplos.New\APLOS\POPResources\Templates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\AplosProject\APLOS\POPResources\Templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10845735-2D2A-465D-AF41-9B9FF83E4621}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41D870E4-8DF3-4822-A41C-3A9631AB26FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -195,13 +195,13 @@
     <t>বেসিক এ্যাপারেলস লিঃ</t>
   </si>
   <si>
+    <t>১৩৫-১৩৮, (২য়-৫ম তলা ) আবদুল্লাহপুর, উত্তরা, ঢাকা-১২৩০</t>
+  </si>
+  <si>
     <t>(বাংলাদেশ শ্রম আইন ২০০৬ এবং সংশোধিত ২০২২ এর ধারা আনুযায়ী)</t>
   </si>
   <si>
     <t>(বাংলাদেশ শ্রম আইন ২০০৬ এবং নতুন সংশোধিত ২০২২ এর ধারা ৪৮ (২) অনুযায়ী প্রসূতিকল্যান সুবিধা হিসাব করিবার ক্ষেত্রে শ্রমিকের সর্বশেষ মাসিক প্রাপ্ত মোট মজুরীকে ২৬ দ্বারা ভাগ করিয়া ০১ দিনের গড় মজুরী নির্ধারন করিতে হইবে। দৈনিক গড় মজুরী (টাকা)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">১৩৫-১৩৮, (২য়-৫ম তলা ) আবদুল্লাহপুর, উত্তরা, ঢাকা-১২৩০ </t>
   </si>
 </sst>
 </file>
@@ -565,6 +565,54 @@
     <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -588,54 +636,6 @@
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -998,24 +998,24 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:Q29"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="17.399999999999999"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="37" style="4" hidden="1" customWidth="1"/>
-    <col min="2" max="2" width="24.109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.140625" style="2" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="19" style="2" customWidth="1"/>
-    <col min="4" max="4" width="19.5546875" style="2" customWidth="1"/>
-    <col min="5" max="5" width="23.33203125" style="2" customWidth="1"/>
-    <col min="6" max="7" width="22.44140625" style="2" customWidth="1"/>
-    <col min="8" max="8" width="26.33203125" style="2" customWidth="1"/>
-    <col min="9" max="10" width="17.88671875" style="2" customWidth="1"/>
+    <col min="4" max="4" width="19.5703125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="23.28515625" style="2" customWidth="1"/>
+    <col min="6" max="7" width="22.42578125" style="2" customWidth="1"/>
+    <col min="8" max="8" width="26.28515625" style="2" customWidth="1"/>
+    <col min="9" max="10" width="17.85546875" style="2" customWidth="1"/>
     <col min="11" max="11" width="19" style="2" customWidth="1"/>
-    <col min="12" max="12" width="18.44140625" style="2" customWidth="1"/>
-    <col min="13" max="13" width="19.5546875" style="2" customWidth="1"/>
-    <col min="14" max="14" width="20.33203125" style="3" customWidth="1"/>
-    <col min="15" max="15" width="20.6640625" style="3" customWidth="1"/>
-    <col min="16" max="16" width="19.44140625" style="3" customWidth="1"/>
-    <col min="17" max="17" width="34.109375" style="3" customWidth="1"/>
-    <col min="18" max="16384" width="9.109375" style="4"/>
+    <col min="12" max="12" width="18.42578125" style="2" customWidth="1"/>
+    <col min="13" max="13" width="19.5703125" style="2" customWidth="1"/>
+    <col min="14" max="14" width="20.28515625" style="3" customWidth="1"/>
+    <col min="15" max="15" width="20.7109375" style="3" customWidth="1"/>
+    <col min="16" max="16" width="19.42578125" style="3" customWidth="1"/>
+    <col min="17" max="17" width="34.140625" style="3" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="4"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="68.25" customHeight="1">
@@ -1024,19 +1024,19 @@
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
-      <c r="G1" s="30" t="s">
+      <c r="G1" s="46" t="s">
         <v>55</v>
       </c>
-      <c r="H1" s="30"/>
-      <c r="I1" s="30"/>
-      <c r="J1" s="30"/>
-      <c r="K1" s="30"/>
-      <c r="L1" s="30"/>
-      <c r="M1" s="30"/>
+      <c r="H1" s="46"/>
+      <c r="I1" s="46"/>
+      <c r="J1" s="46"/>
+      <c r="K1" s="46"/>
+      <c r="L1" s="46"/>
+      <c r="M1" s="46"/>
       <c r="N1" s="1"/>
-      <c r="O1" s="35"/>
-      <c r="P1" s="36"/>
-      <c r="Q1" s="36"/>
+      <c r="O1" s="51"/>
+      <c r="P1" s="52"/>
+      <c r="Q1" s="52"/>
     </row>
     <row r="2" spans="1:17" ht="46.5" customHeight="1">
       <c r="B2" s="5"/>
@@ -1044,166 +1044,166 @@
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
-      <c r="H2" s="31" t="s">
-        <v>58</v>
-      </c>
-      <c r="I2" s="31"/>
-      <c r="J2" s="31"/>
-      <c r="K2" s="31"/>
-      <c r="L2" s="31"/>
-      <c r="M2" s="31"/>
+      <c r="H2" s="47" t="s">
+        <v>56</v>
+      </c>
+      <c r="I2" s="47"/>
+      <c r="J2" s="47"/>
+      <c r="K2" s="47"/>
+      <c r="L2" s="47"/>
+      <c r="M2" s="47"/>
       <c r="N2" s="1"/>
       <c r="O2" s="1"/>
     </row>
     <row r="3" spans="1:17" s="6" customFormat="1" ht="50.25" customHeight="1">
-      <c r="B3" s="33" t="s">
+      <c r="B3" s="49" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="34"/>
-      <c r="D3" s="34"/>
-      <c r="E3" s="34"/>
-      <c r="F3" s="34"/>
-      <c r="G3" s="34"/>
-      <c r="H3" s="34"/>
-      <c r="I3" s="34"/>
-      <c r="J3" s="34"/>
-      <c r="K3" s="34"/>
-      <c r="L3" s="34"/>
-      <c r="M3" s="34"/>
-      <c r="N3" s="34"/>
-      <c r="O3" s="34"/>
-      <c r="P3" s="34"/>
-      <c r="Q3" s="34"/>
+      <c r="C3" s="50"/>
+      <c r="D3" s="50"/>
+      <c r="E3" s="50"/>
+      <c r="F3" s="50"/>
+      <c r="G3" s="50"/>
+      <c r="H3" s="50"/>
+      <c r="I3" s="50"/>
+      <c r="J3" s="50"/>
+      <c r="K3" s="50"/>
+      <c r="L3" s="50"/>
+      <c r="M3" s="50"/>
+      <c r="N3" s="50"/>
+      <c r="O3" s="50"/>
+      <c r="P3" s="50"/>
+      <c r="Q3" s="50"/>
     </row>
     <row r="4" spans="1:17" s="6" customFormat="1" ht="48.75" customHeight="1">
       <c r="A4"/>
-      <c r="B4" s="37" t="s">
-        <v>56</v>
-      </c>
-      <c r="C4" s="37"/>
-      <c r="D4" s="37"/>
-      <c r="E4" s="37"/>
-      <c r="F4" s="37"/>
-      <c r="G4" s="37"/>
-      <c r="H4" s="37"/>
-      <c r="I4" s="37"/>
-      <c r="J4" s="37"/>
-      <c r="K4" s="37"/>
-      <c r="L4" s="37"/>
-      <c r="M4" s="37"/>
-      <c r="N4" s="37"/>
-      <c r="O4" s="37"/>
-      <c r="P4" s="37"/>
-      <c r="Q4" s="37"/>
+      <c r="B4" s="53" t="s">
+        <v>57</v>
+      </c>
+      <c r="C4" s="53"/>
+      <c r="D4" s="53"/>
+      <c r="E4" s="53"/>
+      <c r="F4" s="53"/>
+      <c r="G4" s="53"/>
+      <c r="H4" s="53"/>
+      <c r="I4" s="53"/>
+      <c r="J4" s="53"/>
+      <c r="K4" s="53"/>
+      <c r="L4" s="53"/>
+      <c r="M4" s="53"/>
+      <c r="N4" s="53"/>
+      <c r="O4" s="53"/>
+      <c r="P4" s="53"/>
+      <c r="Q4" s="53"/>
     </row>
     <row r="5" spans="1:17" s="7" customFormat="1" ht="251.25" customHeight="1">
-      <c r="B5" s="43" t="s">
+      <c r="B5" s="35" t="s">
         <v>14</v>
       </c>
-      <c r="C5" s="43" t="s">
+      <c r="C5" s="35" t="s">
         <v>1</v>
       </c>
-      <c r="D5" s="43" t="s">
+      <c r="D5" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="E5" s="43" t="s">
+      <c r="E5" s="35" t="s">
         <v>4</v>
       </c>
-      <c r="F5" s="43" t="s">
+      <c r="F5" s="35" t="s">
         <v>5</v>
       </c>
-      <c r="G5" s="43" t="s">
+      <c r="G5" s="35" t="s">
         <v>6</v>
       </c>
-      <c r="H5" s="43" t="s">
+      <c r="H5" s="35" t="s">
         <v>7</v>
       </c>
-      <c r="I5" s="48" t="s">
-        <v>57</v>
-      </c>
-      <c r="J5" s="49"/>
-      <c r="K5" s="43" t="s">
+      <c r="I5" s="33" t="s">
+        <v>58</v>
+      </c>
+      <c r="J5" s="34"/>
+      <c r="K5" s="35" t="s">
         <v>8</v>
       </c>
-      <c r="L5" s="43" t="s">
+      <c r="L5" s="35" t="s">
         <v>53</v>
       </c>
-      <c r="M5" s="43" t="s">
+      <c r="M5" s="35" t="s">
         <v>11</v>
       </c>
-      <c r="N5" s="41" t="s">
+      <c r="N5" s="44" t="s">
         <v>9</v>
       </c>
-      <c r="O5" s="43" t="s">
+      <c r="O5" s="35" t="s">
         <v>10</v>
       </c>
-      <c r="P5" s="43" t="s">
+      <c r="P5" s="35" t="s">
         <v>54</v>
       </c>
-      <c r="Q5" s="40" t="s">
+      <c r="Q5" s="43" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:17" s="8" customFormat="1" ht="91.2">
-      <c r="B6" s="44"/>
-      <c r="C6" s="44"/>
-      <c r="D6" s="44"/>
-      <c r="E6" s="44"/>
-      <c r="F6" s="44"/>
-      <c r="G6" s="44"/>
-      <c r="H6" s="44"/>
+    <row r="6" spans="1:17" s="8" customFormat="1" ht="93">
+      <c r="B6" s="36"/>
+      <c r="C6" s="36"/>
+      <c r="D6" s="36"/>
+      <c r="E6" s="36"/>
+      <c r="F6" s="36"/>
+      <c r="G6" s="36"/>
+      <c r="H6" s="36"/>
       <c r="I6" s="15" t="s">
         <v>12</v>
       </c>
       <c r="J6" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="K6" s="44"/>
-      <c r="L6" s="44"/>
-      <c r="M6" s="44"/>
-      <c r="N6" s="42"/>
-      <c r="O6" s="44"/>
-      <c r="P6" s="44"/>
-      <c r="Q6" s="39"/>
+      <c r="K6" s="36"/>
+      <c r="L6" s="36"/>
+      <c r="M6" s="36"/>
+      <c r="N6" s="45"/>
+      <c r="O6" s="36"/>
+      <c r="P6" s="36"/>
+      <c r="Q6" s="42"/>
     </row>
     <row r="7" spans="1:17" s="8" customFormat="1" ht="120" customHeight="1">
       <c r="A7" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="B7" s="38" t="s">
+      <c r="B7" s="41" t="s">
         <v>36</v>
       </c>
-      <c r="C7" s="38" t="s">
+      <c r="C7" s="41" t="s">
         <v>37</v>
       </c>
-      <c r="D7" s="38" t="s">
+      <c r="D7" s="41" t="s">
         <v>22</v>
       </c>
-      <c r="E7" s="38" t="s">
+      <c r="E7" s="41" t="s">
         <v>39</v>
       </c>
-      <c r="F7" s="38" t="s">
+      <c r="F7" s="41" t="s">
         <v>38</v>
       </c>
-      <c r="G7" s="38" t="s">
+      <c r="G7" s="41" t="s">
         <v>23</v>
       </c>
-      <c r="H7" s="38" t="s">
+      <c r="H7" s="41" t="s">
         <v>43</v>
       </c>
-      <c r="I7" s="38" t="s">
+      <c r="I7" s="41" t="s">
         <v>42</v>
       </c>
-      <c r="J7" s="38" t="s">
+      <c r="J7" s="41" t="s">
         <v>25</v>
       </c>
-      <c r="K7" s="38" t="s">
+      <c r="K7" s="41" t="s">
         <v>26</v>
       </c>
-      <c r="L7" s="38" t="s">
+      <c r="L7" s="41" t="s">
         <v>24</v>
       </c>
-      <c r="M7" s="38" t="s">
+      <c r="M7" s="41" t="s">
         <v>27</v>
       </c>
       <c r="N7" s="16" t="s">
@@ -1219,18 +1219,18 @@
       <c r="A8" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="B8" s="39"/>
-      <c r="C8" s="39"/>
-      <c r="D8" s="39"/>
-      <c r="E8" s="39"/>
-      <c r="F8" s="39"/>
-      <c r="G8" s="39"/>
-      <c r="H8" s="39"/>
-      <c r="I8" s="39"/>
-      <c r="J8" s="39"/>
-      <c r="K8" s="39"/>
-      <c r="L8" s="39"/>
-      <c r="M8" s="39"/>
+      <c r="B8" s="42"/>
+      <c r="C8" s="42"/>
+      <c r="D8" s="42"/>
+      <c r="E8" s="42"/>
+      <c r="F8" s="42"/>
+      <c r="G8" s="42"/>
+      <c r="H8" s="42"/>
+      <c r="I8" s="42"/>
+      <c r="J8" s="42"/>
+      <c r="K8" s="42"/>
+      <c r="L8" s="42"/>
+      <c r="M8" s="42"/>
       <c r="N8" s="16" t="s">
         <v>21</v>
       </c>
@@ -1247,16 +1247,16 @@
       <c r="E9" s="1"/>
       <c r="F9" s="1"/>
       <c r="G9" s="1"/>
-      <c r="H9" s="50"/>
-      <c r="I9" s="50"/>
-      <c r="J9" s="50"/>
-      <c r="K9" s="50"/>
-      <c r="L9" s="50"/>
-      <c r="M9" s="50"/>
-      <c r="N9" s="50"/>
-      <c r="O9" s="50"/>
-      <c r="P9" s="50"/>
-      <c r="Q9" s="51"/>
+      <c r="H9" s="37"/>
+      <c r="I9" s="37"/>
+      <c r="J9" s="37"/>
+      <c r="K9" s="37"/>
+      <c r="L9" s="37"/>
+      <c r="M9" s="37"/>
+      <c r="N9" s="37"/>
+      <c r="O9" s="37"/>
+      <c r="P9" s="37"/>
+      <c r="Q9" s="38"/>
     </row>
     <row r="10" spans="1:17" s="11" customFormat="1" ht="55.5" customHeight="1">
       <c r="A10" s="10" t="s">
@@ -1277,16 +1277,16 @@
       <c r="F10" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="H10" s="52"/>
-      <c r="I10" s="52"/>
-      <c r="J10" s="52"/>
-      <c r="K10" s="52"/>
-      <c r="L10" s="52"/>
-      <c r="M10" s="52"/>
-      <c r="N10" s="52"/>
-      <c r="O10" s="52"/>
-      <c r="P10" s="52"/>
-      <c r="Q10" s="53"/>
+      <c r="H10" s="39"/>
+      <c r="I10" s="39"/>
+      <c r="J10" s="39"/>
+      <c r="K10" s="39"/>
+      <c r="L10" s="39"/>
+      <c r="M10" s="39"/>
+      <c r="N10" s="39"/>
+      <c r="O10" s="39"/>
+      <c r="P10" s="39"/>
+      <c r="Q10" s="40"/>
     </row>
     <row r="11" spans="1:17" s="8" customFormat="1" ht="56.25" customHeight="1">
       <c r="A11" s="8" t="s">
@@ -1307,16 +1307,16 @@
       <c r="F11" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="H11" s="52"/>
-      <c r="I11" s="52"/>
-      <c r="J11" s="52"/>
-      <c r="K11" s="52"/>
-      <c r="L11" s="52"/>
-      <c r="M11" s="52"/>
-      <c r="N11" s="52"/>
-      <c r="O11" s="52"/>
-      <c r="P11" s="52"/>
-      <c r="Q11" s="53"/>
+      <c r="H11" s="39"/>
+      <c r="I11" s="39"/>
+      <c r="J11" s="39"/>
+      <c r="K11" s="39"/>
+      <c r="L11" s="39"/>
+      <c r="M11" s="39"/>
+      <c r="N11" s="39"/>
+      <c r="O11" s="39"/>
+      <c r="P11" s="39"/>
+      <c r="Q11" s="40"/>
     </row>
     <row r="12" spans="1:17" s="8" customFormat="1" ht="60" customHeight="1">
       <c r="B12" s="19"/>
@@ -1324,16 +1324,16 @@
       <c r="D12" s="19"/>
       <c r="E12" s="19"/>
       <c r="F12" s="19"/>
-      <c r="H12" s="52"/>
-      <c r="I12" s="52"/>
-      <c r="J12" s="52"/>
-      <c r="K12" s="52"/>
-      <c r="L12" s="52"/>
-      <c r="M12" s="52"/>
-      <c r="N12" s="52"/>
-      <c r="O12" s="52"/>
-      <c r="P12" s="52"/>
-      <c r="Q12" s="53"/>
+      <c r="H12" s="39"/>
+      <c r="I12" s="39"/>
+      <c r="J12" s="39"/>
+      <c r="K12" s="39"/>
+      <c r="L12" s="39"/>
+      <c r="M12" s="39"/>
+      <c r="N12" s="39"/>
+      <c r="O12" s="39"/>
+      <c r="P12" s="39"/>
+      <c r="Q12" s="40"/>
     </row>
     <row r="13" spans="1:17" s="8" customFormat="1" ht="60" hidden="1" customHeight="1">
       <c r="B13" s="19"/>
@@ -1341,16 +1341,16 @@
       <c r="D13" s="19"/>
       <c r="E13" s="19"/>
       <c r="F13" s="19"/>
-      <c r="H13" s="52"/>
-      <c r="I13" s="52"/>
-      <c r="J13" s="52"/>
-      <c r="K13" s="52"/>
-      <c r="L13" s="52"/>
-      <c r="M13" s="52"/>
-      <c r="N13" s="52"/>
-      <c r="O13" s="52"/>
-      <c r="P13" s="52"/>
-      <c r="Q13" s="53"/>
+      <c r="H13" s="39"/>
+      <c r="I13" s="39"/>
+      <c r="J13" s="39"/>
+      <c r="K13" s="39"/>
+      <c r="L13" s="39"/>
+      <c r="M13" s="39"/>
+      <c r="N13" s="39"/>
+      <c r="O13" s="39"/>
+      <c r="P13" s="39"/>
+      <c r="Q13" s="40"/>
     </row>
     <row r="14" spans="1:17" s="8" customFormat="1" ht="60" hidden="1" customHeight="1">
       <c r="B14" s="19"/>
@@ -1358,16 +1358,16 @@
       <c r="D14" s="19"/>
       <c r="E14" s="19"/>
       <c r="F14" s="19"/>
-      <c r="H14" s="52"/>
-      <c r="I14" s="52"/>
-      <c r="J14" s="52"/>
-      <c r="K14" s="52"/>
-      <c r="L14" s="52"/>
-      <c r="M14" s="52"/>
-      <c r="N14" s="52"/>
-      <c r="O14" s="52"/>
-      <c r="P14" s="52"/>
-      <c r="Q14" s="53"/>
+      <c r="H14" s="39"/>
+      <c r="I14" s="39"/>
+      <c r="J14" s="39"/>
+      <c r="K14" s="39"/>
+      <c r="L14" s="39"/>
+      <c r="M14" s="39"/>
+      <c r="N14" s="39"/>
+      <c r="O14" s="39"/>
+      <c r="P14" s="39"/>
+      <c r="Q14" s="40"/>
     </row>
     <row r="15" spans="1:17" s="8" customFormat="1" ht="60" hidden="1" customHeight="1">
       <c r="B15" s="19"/>
@@ -1375,16 +1375,16 @@
       <c r="D15" s="19"/>
       <c r="E15" s="19"/>
       <c r="F15" s="19"/>
-      <c r="H15" s="52"/>
-      <c r="I15" s="52"/>
-      <c r="J15" s="52"/>
-      <c r="K15" s="52"/>
-      <c r="L15" s="52"/>
-      <c r="M15" s="52"/>
-      <c r="N15" s="52"/>
-      <c r="O15" s="52"/>
-      <c r="P15" s="52"/>
-      <c r="Q15" s="53"/>
+      <c r="H15" s="39"/>
+      <c r="I15" s="39"/>
+      <c r="J15" s="39"/>
+      <c r="K15" s="39"/>
+      <c r="L15" s="39"/>
+      <c r="M15" s="39"/>
+      <c r="N15" s="39"/>
+      <c r="O15" s="39"/>
+      <c r="P15" s="39"/>
+      <c r="Q15" s="40"/>
     </row>
     <row r="16" spans="1:17" s="8" customFormat="1" ht="24.75" customHeight="1">
       <c r="B16" s="26"/>
@@ -1392,16 +1392,16 @@
       <c r="D16" s="27"/>
       <c r="E16" s="27"/>
       <c r="F16" s="27"/>
-      <c r="H16" s="52"/>
-      <c r="I16" s="52"/>
-      <c r="J16" s="52"/>
-      <c r="K16" s="52"/>
-      <c r="L16" s="52"/>
-      <c r="M16" s="52"/>
-      <c r="N16" s="52"/>
-      <c r="O16" s="52"/>
-      <c r="P16" s="52"/>
-      <c r="Q16" s="53"/>
+      <c r="H16" s="39"/>
+      <c r="I16" s="39"/>
+      <c r="J16" s="39"/>
+      <c r="K16" s="39"/>
+      <c r="L16" s="39"/>
+      <c r="M16" s="39"/>
+      <c r="N16" s="39"/>
+      <c r="O16" s="39"/>
+      <c r="P16" s="39"/>
+      <c r="Q16" s="40"/>
     </row>
     <row r="17" spans="2:17" s="8" customFormat="1" ht="24.75" customHeight="1">
       <c r="B17" s="28"/>
@@ -1527,10 +1527,10 @@
       <c r="Q23" s="12"/>
     </row>
     <row r="24" spans="2:17" s="8" customFormat="1" ht="30.75" customHeight="1">
-      <c r="B24" s="32" t="s">
+      <c r="B24" s="48" t="s">
         <v>45</v>
       </c>
-      <c r="C24" s="32"/>
+      <c r="C24" s="48"/>
       <c r="D24" s="21"/>
       <c r="E24" s="22"/>
       <c r="F24" s="2"/>
@@ -1539,24 +1539,24 @@
       </c>
       <c r="H24" s="21"/>
       <c r="I24" s="22"/>
-      <c r="J24" s="32" t="s">
+      <c r="J24" s="48" t="s">
         <v>48</v>
       </c>
-      <c r="K24" s="32"/>
+      <c r="K24" s="48"/>
       <c r="L24" s="21"/>
       <c r="M24" s="22"/>
       <c r="N24" s="22"/>
-      <c r="O24" s="32" t="s">
+      <c r="O24" s="48" t="s">
         <v>49</v>
       </c>
-      <c r="P24" s="32"/>
+      <c r="P24" s="48"/>
       <c r="Q24" s="1"/>
     </row>
-    <row r="25" spans="2:17" s="11" customFormat="1" ht="20.399999999999999">
-      <c r="B25" s="45" t="s">
+    <row r="25" spans="2:17" s="11" customFormat="1" ht="20.25">
+      <c r="B25" s="30" t="s">
         <v>46</v>
       </c>
-      <c r="C25" s="45"/>
+      <c r="C25" s="30"/>
       <c r="D25" s="23"/>
       <c r="E25" s="24"/>
       <c r="F25" s="2"/>
@@ -1565,17 +1565,17 @@
       </c>
       <c r="H25" s="23"/>
       <c r="I25" s="24"/>
-      <c r="J25" s="46" t="s">
+      <c r="J25" s="31" t="s">
         <v>51</v>
       </c>
-      <c r="K25" s="46"/>
+      <c r="K25" s="31"/>
       <c r="L25" s="23"/>
       <c r="M25" s="24"/>
       <c r="N25" s="24"/>
-      <c r="O25" s="47" t="s">
+      <c r="O25" s="32" t="s">
         <v>52</v>
       </c>
-      <c r="P25" s="47"/>
+      <c r="P25" s="32"/>
       <c r="Q25" s="12"/>
     </row>
     <row r="26" spans="2:17" s="11" customFormat="1">
@@ -1599,6 +1599,29 @@
     <row r="29" spans="2:17" ht="31.5" customHeight="1"/>
   </sheetData>
   <mergeCells count="39">
+    <mergeCell ref="G1:M1"/>
+    <mergeCell ref="H2:M2"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="O24:P24"/>
+    <mergeCell ref="B3:Q3"/>
+    <mergeCell ref="O1:Q1"/>
+    <mergeCell ref="B4:Q4"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="G7:G8"/>
+    <mergeCell ref="E7:E8"/>
+    <mergeCell ref="L7:L8"/>
+    <mergeCell ref="J7:J8"/>
+    <mergeCell ref="F7:F8"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="C7:C8"/>
+    <mergeCell ref="D7:D8"/>
+    <mergeCell ref="H7:H8"/>
+    <mergeCell ref="Q5:Q6"/>
+    <mergeCell ref="N5:N6"/>
+    <mergeCell ref="O5:O6"/>
+    <mergeCell ref="M7:M8"/>
+    <mergeCell ref="K7:K8"/>
+    <mergeCell ref="I7:I8"/>
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="J25:K25"/>
     <mergeCell ref="O25:P25"/>
@@ -1615,29 +1638,6 @@
     <mergeCell ref="B5:B6"/>
     <mergeCell ref="P5:P6"/>
     <mergeCell ref="H9:Q16"/>
-    <mergeCell ref="H7:H8"/>
-    <mergeCell ref="Q5:Q6"/>
-    <mergeCell ref="N5:N6"/>
-    <mergeCell ref="O5:O6"/>
-    <mergeCell ref="M7:M8"/>
-    <mergeCell ref="K7:K8"/>
-    <mergeCell ref="I7:I8"/>
-    <mergeCell ref="G1:M1"/>
-    <mergeCell ref="H2:M2"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="O24:P24"/>
-    <mergeCell ref="B3:Q3"/>
-    <mergeCell ref="O1:Q1"/>
-    <mergeCell ref="B4:Q4"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="G7:G8"/>
-    <mergeCell ref="E7:E8"/>
-    <mergeCell ref="L7:L8"/>
-    <mergeCell ref="J7:J8"/>
-    <mergeCell ref="F7:F8"/>
-    <mergeCell ref="B7:B8"/>
-    <mergeCell ref="C7:C8"/>
-    <mergeCell ref="D7:D8"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.25" top="0.25" bottom="0.5" header="0" footer="0"/>
   <pageSetup paperSize="9" scale="52" fitToHeight="0" orientation="landscape" r:id="rId1"/>
